--- a/CBT_2024_1회/산업안전기사_2024_1회_문항등록.xlsx
+++ b/CBT_2024_1회/산업안전기사_2024_1회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AH5" s="32" t="inlineStr">
         <is>
-          <t>① 2.5G 4/10 은 녹색으로 안내에 쓴다.&lt;br&gt;③ 5Y 8.5/12 는 노란색으로 경고에 쓴다.&lt;br&gt;④ 7.5R 4/14 는 빨간색으로 금지·경고에 쓴다.</t>
+          <t>① 2.5G 4/10은 녹색으로 안내에 쓴다.&lt;br&gt;③ 5Y 8.5/12는 노란색으로 경고에 쓴다.&lt;br&gt;④ 7.5R 4/14는 빨간색으로 금지·경고에 쓴다.</t>
         </is>
       </c>
       <c r="AI5" s="32" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AG7" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;브레인스토밍&lt;/strong&gt;이다. &lt;strong&gt;비판하지 않고 자유롭게 많이 낸 뒤 결합·개선&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;브레인스토밍의 4원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비판 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남의 생각을 깎아내리지 않는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자유 분방&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;엉뚱해도 좋다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대량 발언&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질보다 양&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수정 발언(결합과 개선)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남의 생각에 얹어도 좋다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;브레인스토밍&lt;/strong&gt;이다. &lt;strong&gt;비판하지 않고 자유롭게 많이 낸 뒤 결합·개선&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;브레인스토밍의 4원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비판 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남의 생각을 깎아내리지 않는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자유 분방&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;엉뚱해도 좋다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대량 발언&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질보다 양&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수정 발언(결합과 개선)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;남의 생각에 얹어도 좋다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH7" s="32" t="inlineStr">
@@ -2476,7 +2476,11 @@
           <t>인간의 행동특성과 관련한 레빈의 법칙(Lewin)중 P가 의미하는 것은?</t>
         </is>
       </c>
-      <c r="V11" s="32" t="inlineStr"/>
+      <c r="V11" s="32" t="inlineStr">
+        <is>
+          <t>B = f (P · E)</t>
+        </is>
+      </c>
       <c r="W11" s="32" t="inlineStr"/>
       <c r="X11" s="32" t="inlineStr">
         <is>
@@ -2507,17 +2511,17 @@
       </c>
       <c r="AG11" s="32" t="inlineStr">
         <is>
-          <t>$B = f ( P \cdot E )$ 에서 &lt;strong&gt;P 는 person&lt;/strong&gt;이다. &lt;strong&gt;나이 · 경험 · 성격 · 지능 · 심신 상태&lt;/strong&gt;를 뜻한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈의 법칙 $B = f ( P \cdot E )$&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior 행동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;겉으로 드러나는 행동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function 함수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;P 와 E 가 함께 정한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person 사람&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;나이 · 경험 · 성격 · 지능 · 심신 상태&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment 환경&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간관계 · 작업환경 · 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$B = f ( P \cdot E )$에서 &lt;strong&gt;P는 person&lt;/strong&gt;이다. &lt;strong&gt;나이 · 경험 · 성격 · 지능 · 심신 상태&lt;/strong&gt;를 뜻한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈의 법칙 $B = f ( P \cdot E )$&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior 행동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;겉으로 드러나는 행동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function 함수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;P와 E가 함께 정한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person 사람&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;나이 · 경험 · 성격 · 지능 · 심신 상태&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment 환경&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간관계 · 작업환경 · 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH11" s="32" t="inlineStr">
         <is>
-          <t>② 인간의 행동은 B 다.&lt;br&gt;③ 심리에 영향을 주는 인간관계는 E 다.&lt;br&gt;④ 심리에 영향을 미치는 작업환경도 E 다.</t>
+          <t>② 인간의 행동은 B다.&lt;br&gt;③ 심리에 영향을 주는 인간관계는 E다.&lt;br&gt;④ 심리에 영향을 미치는 작업환경도 E다.</t>
         </is>
       </c>
       <c r="AI11" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;레빈(Lewin)의 인간 행동 법칙&lt;/strong&gt;&lt;br&gt;이 식의 요지는 &lt;strong&gt;행동은 사람 탓만도 환경 탓만도 아니다&lt;/strong&gt;라는 것이다. &lt;strong&gt;사람은 쉽게 못 바꾸지만 환경은 바꿀 수&lt;/strong&gt; 있으므로, 안전관리는 &lt;strong&gt;E 를 손보는 쪽&lt;/strong&gt;으로 간다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;P 는 사람, E 는 환경&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;레빈(Lewin)의 인간 행동 법칙&lt;/strong&gt;&lt;br&gt;이 식의 요지는 &lt;strong&gt;행동은 사람 탓만도 환경 탓만도 아니다&lt;/strong&gt;라는 것이다. &lt;strong&gt;사람은 쉽게 못 바꾸지만 환경은 바꿀 수&lt;/strong&gt; 있으므로, 안전관리는 &lt;strong&gt;E를 손보는 쪽&lt;/strong&gt;으로 간다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;P는 사람, E는 환경&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2779,7 @@
       </c>
       <c r="AI13" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산업안전보건법 시행규칙 별표5 — 교육대상별 교육내용&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「산재보험 제도」&lt;/strong&gt;는 &lt;strong&gt;처음 들어온 사람에게 알려 주는 제도 안내&lt;/strong&gt;다. 정기교육은 &lt;strong&gt;일하면서 되풀이해 익힐 것&lt;/strong&gt;을 다룬다는 점에서 결이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산재보험 제도는 채용 시 교육&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 이 문항은 &lt;u&gt;개정 전 기준으로 출제&lt;/u&gt; 되었다. 현행 별표5 의 관리감독자 정기교육에는 &lt;u&gt;위험성 평가에 관한 사항 · 현장근로자와의 의사소통능력 및 강의능력 등 안전보건교육 능력 배양에 관한 사항&lt;/u&gt;이 들어가 있다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행규칙 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건법 시행규칙 별표 5&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
+          <t>&lt;strong&gt;산업안전보건법 시행규칙 별표5 — 교육대상별 교육내용&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「산재보험 제도」&lt;/strong&gt;는 &lt;strong&gt;처음 들어온 사람에게 알려 주는 제도 안내&lt;/strong&gt;다. 정기교육은 &lt;strong&gt;일하면서 되풀이해 익힐 것&lt;/strong&gt;을 다룬다는 점에서 결이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산재보험 제도는 채용 시 교육&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 이 문항은 &lt;u&gt;개정 전 기준으로 출제&lt;/u&gt; 되었다. 현행 별표5의 관리감독자 정기교육에는 &lt;u&gt;위험성 평가에 관한 사항 · 현장근로자와의 의사소통능력 및 강의능력 등 안전보건교육 능력 배양에 관한 사항&lt;/u&gt;이 들어가 있다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건법 시행규칙 시행 2026. 8. 1.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EB%B2%95%EC%8B%9C%ED%96%89%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건법 시행규칙 별표 5&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -2894,17 +2898,17 @@
       </c>
       <c r="AG14" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;직장의 실정에 맞는 구체적이고 실제적인 지도&lt;/strong&gt;가 OJT 의 장점이다. 나머지 셋은 모두 Off JT 의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT 와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT (직장 안)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT (직장 밖)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직장 실정에 맞다 · 개개인에 맞춘다 · 곧바로 실무에 쓴다 · 효과가 곧 나타난다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;많은 사람을 한꺼번에 · 전문가 초빙 · 특별한 교재와 설비 · 다른 직장 사람과 교류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;단점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;한 번에 많이 못 한다 · 상사의 능력에 좌우된다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;현장에 바로 맞지 않을 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;직장의 실정에 맞는 구체적이고 실제적인 지도&lt;/strong&gt;가 OJT의 장점이다. 나머지 셋은 모두 Off JT의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT (직장 안)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT (직장 밖)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직장 실정에 맞다 · 개개인에 맞춘다 · 곧바로 실무에 쓴다 · 효과가 곧 나타난다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;많은 사람을 한꺼번에 · 전문가 초빙 · 특별한 교재와 설비 · 다른 직장 사람과 교류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;단점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;한 번에 많이 못 한다 · 상사의 능력에 좌우된다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;현장에 바로 맞지 않을 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH14" s="32" t="inlineStr">
         <is>
-          <t>① 특별한 교재·교구·설비를 쓰는 것은 Off JT 의 장점이다.&lt;br&gt;② 외부 전문가 위촉도 Off JT 다.&lt;br&gt;④ 다수에 대한 조직적 훈련도 Off JT 다.</t>
+          <t>① 특별한 교재·교구·설비를 쓰는 것은 Off JT의 장점이다.&lt;br&gt;② 외부 전문가 위촉도 Off JT다.&lt;br&gt;④ 다수에 대한 조직적 훈련도 Off JT다.</t>
         </is>
       </c>
       <c r="AI14" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OJT 와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「많이 · 전문가 · 특별한 설비 · 교류」 넷은 모두 Off JT&lt;/strong&gt;다. OJT 의 장점은 &lt;strong&gt;「맞춤」과 「즉시」&lt;/strong&gt; 두 낱말로 모인다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;맞춤과 즉시는 OJT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;OJT와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「많이 · 전문가 · 특별한 설비 · 교류」 넷은 모두 Off JT&lt;/strong&gt;다. OJT의 장점은 &lt;strong&gt;「맞춤」과 「즉시」&lt;/strong&gt; 두 낱말로 모인다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;맞춤과 즉시는 OJT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3152,17 +3156,17 @@
       </c>
       <c r="AG16" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Job Standardization Training&lt;/strong&gt;은 TWI 에 없다. 넷은 &lt;strong&gt;JIT · JMT · JRT · JST(안전)&lt;/strong&gt; 인데, 마지막 &lt;strong&gt;JST 는 Job Safety Training&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;TWI 의 네 가지 과정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;과정&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영문&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 가르치나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JIT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Instruction Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업을 가르치는 법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JMT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Method Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업을 개선하는 법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JRT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Relation Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람을 다루는 법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JST&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Safety Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전하게 일하는 법&lt;/u&gt; — Standardization 이 아니다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;Job Standardization Training&lt;/strong&gt;은 TWI에 없다. 넷은 &lt;strong&gt;JIT · JMT · JRT · JST(안전)&lt;/strong&gt; 인데, 마지막 &lt;strong&gt;JST는 Job Safety Training&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;TWI의 네 가지 과정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;과정&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영문&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 가르치나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JIT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Instruction Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업을 가르치는 법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JMT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Method Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업을 개선하는 법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JRT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Relation Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람을 다루는 법&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JST&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Safety Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전하게 일하는 법&lt;/u&gt; — Standardization이 아니다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH16" s="32" t="inlineStr">
         <is>
-          <t>① Job Method Training(JMT)은 TWI 의 과정이다.&lt;br&gt;② Job Relation Training(JRT)도 그렇다.&lt;br&gt;③ Job Instruction Training(JIT)도 그렇다.</t>
+          <t>① Job Method Training(JMT)은 TWI의 과정이다.&lt;br&gt;② Job Relation Training(JRT)도 그렇다.&lt;br&gt;③ Job Instruction Training(JIT)도 그렇다.</t>
         </is>
       </c>
       <c r="AI16" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;TWI(Training Within Industry)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;TWI 는 관리감독자를 위한 정형교육&lt;/strong&gt;으로 &lt;strong&gt;1회 10시간, 하루 2시간씩 5일&lt;/strong&gt;에 걸쳐 한다. 갈림길은 &lt;strong&gt;JST 의 S 가 Standardization 이 아니라 Safety&lt;/strong&gt;라는 데 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가르치고 · 고치고 · 다루고 · 안전하게&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;TWI(Training Within Industry)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;TWI는 관리감독자를 위한 정형교육&lt;/strong&gt;으로 &lt;strong&gt;1회 10시간, 하루 2시간씩 5일&lt;/strong&gt;에 걸쳐 한다. 갈림길은 &lt;strong&gt;JST의 S가 Standardization이 아니라 Safety&lt;/strong&gt;라는 데 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가르치고 · 고치고 · 다루고 · 안전하게&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3547,7 @@
       </c>
       <c r="AG19" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1 : 29 : 300&lt;/strong&gt;이므로 경상 29 가 58 이면 &lt;strong&gt;2배&lt;/strong&gt;다. 무상해 사고는 $300 \times 2 = 600$ 건이다.&lt;img src="safe_A_2024_01_017_exp1.png"&gt;&lt;em&gt;하인리히의 1 : 29 : 300 — 아래로 갈수록 넓어진다&lt;/em&gt;</t>
+          <t>&lt;strong&gt;1 : 29 : 300&lt;/strong&gt;이므로 경상 29가 58 이면 &lt;strong&gt;2배&lt;/strong&gt;다. 무상해 사고는 $300 \times 2 = 600$ 건이다.&lt;img src="safe_A_2024_01_017_exp1.png"&gt;&lt;em&gt;하인리히의 1 : 29 : 300 — 아래로 갈수록 넓어진다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH19" s="32" t="inlineStr">
@@ -3801,7 +3805,7 @@
       </c>
       <c r="AG21" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;잠재재해 위험요인의 색출&lt;/strong&gt;이 재해조사 단계의 일이다. 나머지 셋은 &lt;strong&gt;긴급처리&lt;/strong&gt; 단계다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해발생 시 조치순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;하는 일&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;긴급처리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기계 정지 → 피해자 응급조치 → 관계자 통보 → 2차 재해 방지 → 현장 보존&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해조사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잠재 위험요인의 색출&lt;/u&gt; · 사실 수집&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;원인강구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사람 · 물체 · 관리의 세 갈래로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대책수립&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이유가 분명한 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대책실시계획&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5W1H 로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;실시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;7&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;잠재재해 위험요인의 색출&lt;/strong&gt;이 재해조사 단계의 일이다. 나머지 셋은 &lt;strong&gt;긴급처리&lt;/strong&gt; 단계다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해발생 시 조치순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;하는 일&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;긴급처리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기계 정지 → 피해자 응급조치 → 관계자 통보 → 2차 재해 방지 → 현장 보존&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해조사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잠재 위험요인의 색출&lt;/u&gt; · 사실 수집&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;원인강구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사람 · 물체 · 관리의 세 갈래로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대책수립&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이유가 분명한 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대책실시계획&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5W1H로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;실시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;7&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH21" s="32" t="inlineStr">
@@ -3811,7 +3815,7 @@
       </c>
       <c r="AI21" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;재해발생 시의 조치순서&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;긴급처리 안에서도 순서&lt;/strong&gt;가 있다 — &lt;strong&gt;기계를 세우고 → 사람을 살리고 → 알리고 → 2차 재해를 막고 → 현장을 보존&lt;/strong&gt; 한다. &lt;strong&gt;사람이 먼저, 현장 보존은 나중&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;긴급 · 조사 · 원인 · 대책 · 계획 · 실시 · 평가&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;재해발생 시의 조치순서&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;긴급처리 안에서도 순서&lt;/strong&gt;가 있다 — &lt;strong&gt;기계를 세우고 → 사람을 살리고 → 알리고 → 2차 재해를 막고 → 현장을 보존&lt;/strong&gt;한다. &lt;strong&gt;사람이 먼저, 현장 보존은 나중&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;긴급 · 조사 · 원인 · 대책 · 계획 · 실시 · 평가&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3930,12 +3934,12 @@
       </c>
       <c r="AG22" s="32" t="inlineStr">
         <is>
-          <t>도수율은 $\dfrac{12}{1 {,} 200 {,} 000} \times 10^{6} = 10$ 이다. 종합재해지수는 $\mathrm{FSI} = \sqrt{\text{도수율} \times \text{강도율}} = \sqrt{10 \times 2.5} = \sqrt{25} = 5.0$ 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해율 세 가지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율 FR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{재해건수}}{\text{연근로시간}} \times 10^{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 자주&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율 SR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{근로손실일수}}{\text{연근로시간}} \times 10^{3}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 심하게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;종합재해지수 FSI&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\sqrt{FR \times SR}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;둘의 기하평균&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>도수율은 $\dfrac{12}{1 {,} 200 {,} 000} \times 10^{6} = 10$이다. 종합재해지수는 $\mathrm{FSI} = \sqrt{\text{도수율} \times \text{강도율}} = \sqrt{10 \times 2.5} = \sqrt{25} = 5.0$이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해율 세 가지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율 FR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{재해건수}}{\text{연근로시간}} \times 10^{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 자주&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율 SR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{근로손실일수}}{\text{연근로시간}} \times 10^{3}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 심하게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;종합재해지수 FSI&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\sqrt{FR \times SR}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;둘의 기하평균&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH22" s="32" t="inlineStr">
         <is>
-          <t>① 1.6 은 계산과 맞지 않는다.&lt;br&gt;③ 27.6 도 맞지 않는다.&lt;br&gt;④ 230 도 맞지 않는다.</t>
+          <t>① 1.6은 계산과 맞지 않는다.&lt;br&gt;③ 27.6 도 맞지 않는다.&lt;br&gt;④ 230 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI22" s="32" t="inlineStr">
@@ -4064,7 +4068,7 @@
       </c>
       <c r="AH23" s="32" t="inlineStr">
         <is>
-          <t>① critical set 은 FTA 의 정식 용어가 아니다.&lt;br&gt;② 「minimal gate」라는 용어는 없다.&lt;br&gt;④ Boolean indicated cut set 은 불 대수로 정리하기 전의 컷셋을 가리키는 말이다.</t>
+          <t>① critical set은 FTA의 정식 용어가 아니다.&lt;br&gt;② 「minimal gate」라는 용어는 없다.&lt;br&gt;④ Boolean indicated cut set은 불 대수로 정리하기 전의 컷셋을 가리키는 말이다.</t>
         </is>
       </c>
       <c r="AI23" s="32" t="inlineStr">
@@ -4192,7 +4196,7 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;㉠ → ㉣ → ㉡ → ㉢&lt;/strong&gt;이다. &lt;strong&gt;무엇을 볼지 정하고 → 원인을 캐고 → 그림으로 그려 분석하고 → 고칠 계획을 세운다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 에 의한 재해사례 연구순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;하는 일&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상사상의 선정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;막고 싶은 재해를 톱에 놓는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;각 사상의 재해원인 규명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 단계씩 아래로 캐내려간다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FT도 작성 및 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;게이트로 이어 그리고 컷셋을 구한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개선 계획의 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중요도가 큰 곳부터 고친다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;㉠ → ㉣ → ㉡ → ㉢&lt;/strong&gt;이다. &lt;strong&gt;무엇을 볼지 정하고 → 원인을 캐고 → 그림으로 그려 분석하고 → 고칠 계획을 세운다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA에 의한 재해사례 연구순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;순서&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;하는 일&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상사상의 선정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;막고 싶은 재해를 톱에 놓는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;각 사상의 재해원인 규명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 단계씩 아래로 캐내려간다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FT도 작성 및 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;게이트로 이어 그리고 컷셋을 구한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개선 계획의 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중요도가 큰 곳부터 고친다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
@@ -4202,7 +4206,7 @@
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 진행순서&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;원인을 캐야 그림을 그릴 수 있고, 그림을 분석해야 무엇을 고칠지 알 수&lt;/strong&gt; 있다. &lt;strong&gt;개선 계획이 언제나 마지막&lt;/strong&gt;이라는 것만 잡아도 보기 둘이 걸러진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;정상사상 · 원인 규명 · FT도 · 개선 계획&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 진행순서&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;원인을 캐야 그림을 그릴 수 있고, 그림을 분석해야 무엇을 고칠지 알 수&lt;/strong&gt; 있다. &lt;strong&gt;개선 계획이 언제나 마지막&lt;/strong&gt;이라는 것만 잡아도 보기 둘이 걸러진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;정상사상 · 원인 규명 · FT도 · 개선 계획&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4325,7 @@
       </c>
       <c r="AG25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지식에 기초한 행동&lt;/strong&gt;이다. &lt;strong&gt;처음 겪는 상황에서 따져 판단하다가 잘못&lt;/strong&gt; 하는 경우다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;라스무센(Rasmussen)의 인간행동 3분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;행동&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;언제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;오류의 성격&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기능(숙련) 기반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;몸에 밴 일을 할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;깜빡함(slip · lapse)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;규칙 기반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아는 규칙을 적용할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;규칙을 잘못 고름&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지식 기반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;처음 겪는 상황에서 따질 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분석·의사결정의 오류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;지식에 기초한 행동&lt;/strong&gt;이다. &lt;strong&gt;처음 겪는 상황에서 따져 판단하다가 잘못&lt;/strong&gt;하는 경우다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;라스무센(Rasmussen)의 인간행동 3분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;행동&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;언제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;오류의 성격&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기능(숙련) 기반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;몸에 밴 일을 할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;깜빡함(slip · lapse)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;규칙 기반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아는 규칙을 적용할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;규칙을 잘못 고름&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지식 기반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;처음 겪는 상황에서 따질 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분석·의사결정의 오류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH25" s="32" t="inlineStr">
@@ -4826,7 +4830,7 @@
       </c>
       <c r="AH29" s="32" t="inlineStr">
         <is>
-          <t>① 초정밀작업은 650 이 아니라 750 [lux] 이상이다.&lt;br&gt;② ㉠과 ㉡ 둘 다 어긋난다.&lt;br&gt;④ 보통작업은 250 이 아니라 150 [lux] 이상이다.</t>
+          <t>① 초정밀작업은 650이 아니라 750 [lux] 이상이다.&lt;br&gt;② ㉠과 ㉡ 둘 다 어긋난다.&lt;br&gt;④ 보통작업은 250이 아니라 150 [lux] 이상이다.</t>
         </is>
       </c>
       <c r="AI29" s="32" t="inlineStr">
@@ -5079,12 +5083,12 @@
       </c>
       <c r="AG31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;「안전 종류」&lt;/strong&gt;라는 항목은 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;SSPP 에 담는 아홉 가지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계획의 개요&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전 조직&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계약 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관련 부문과의 조정&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전 기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전 해석&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전성 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전 데이터의 수집과 분석&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경과와 결과의 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;「안전 종류」&lt;/strong&gt;라는 항목은 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;SSPP에 담는 아홉 가지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계획의 개요&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전 조직&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계약 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관련 부문과의 조정&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전 기준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전 해석&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전성 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전 데이터의 수집과 분석&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경과와 결과의 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① 안전 조직은 SSPP 에 담는다.&lt;br&gt;② 안전 기준도 그렇다.&lt;br&gt;④ 안전성 평가도 그렇다.</t>
+          <t>① 안전 조직은 SSPP에 담는다.&lt;br&gt;② 안전 기준도 그렇다.&lt;br&gt;④ 안전성 평가도 그렇다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
@@ -5174,7 +5178,7 @@
       </c>
       <c r="U32" s="32" t="inlineStr">
         <is>
-          <t>다음 시스템의 신뢰도는 얼마인가? (단, 각 요소의 신뢰도는 a, b가 각 0.8, c, d 가 각 0.6이다.)</t>
+          <t>다음 시스템의 신뢰도는 얼마인가? (단, 각 요소의 신뢰도는 a, b가 각 0.8, c, d가 각 0.6이다.)</t>
         </is>
       </c>
       <c r="V32" s="32" t="inlineStr"/>
@@ -5212,17 +5216,17 @@
       </c>
       <c r="AG32" s="32" t="inlineStr">
         <is>
-          <t>$b$ 와 $c$ 가 병렬이므로 $1 - ( 1 - 0.8 ) ( 1 - 0.6 ) = 1 - 0.08 = 0.92$ 다. 전체는 $0.8 \times 0.92 \times 0.6 = 0.4416$ 이다.</t>
+          <t>$b$와 $c$가 병렬이므로 $1 - ( 1 - 0.8 ) ( 1 - 0.6 ) = 1 - 0.08 = 0.92$다. 전체는 $0.8 \times 0.92 \times 0.6 = 0.4416$이다.</t>
         </is>
       </c>
       <c r="AH32" s="32" t="inlineStr">
         <is>
-          <t>① 0.2245 는 계산과 맞지 않는다.&lt;br&gt;② 0.3754 도 맞지 않는다.&lt;br&gt;④ 0.5756 도 맞지 않는다.</t>
+          <t>① 0.2245는 계산과 맞지 않는다.&lt;br&gt;② 0.3754 도 맞지 않는다.&lt;br&gt;④ 0.5756 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI32" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;직렬·병렬 결합의 신뢰도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;병렬을 먼저 하나로 묶고 나서 직렬로 곱한다&lt;/strong&gt;. 직렬은 $R_{1} R_{2}$, 병렬은 $1 - ( 1 - R_{1} ) ( 1 - R_{2} )$ 다. &lt;strong&gt;병렬은 어느 하나만 살아도 되므로 신뢰도가 올라간다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;병렬 먼저 묶고 직렬로 곱한다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;직렬·병렬 결합의 신뢰도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;병렬을 먼저 하나로 묶고 나서 직렬로 곱한다&lt;/strong&gt;. 직렬은 $R_{1} R_{2}$, 병렬은 $1 - ( 1 - R_{1} ) ( 1 - R_{2} )$다. &lt;strong&gt;병렬은 어느 하나만 살아도 되므로 신뢰도가 올라간다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;병렬 먼저 묶고 직렬로 곱한다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5345,17 +5349,17 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>두 병렬을 먼저 묶는다. 앞은 $1 - ( 1 - 0.75 ) ( 1 - 0.85 ) = 0.9625$, 뒤는 $1 - ( 1 - 0.80 ) ( 1 - 0.90 ) = 0.98$ 이다. 전체는 $0.80 \times 0.90 \times 0.9625 \times 0.98 \times 0.85 \fallingdotseq 0.578$ 이다.</t>
+          <t>두 병렬을 먼저 묶는다. 앞은 $1 - ( 1 - 0.75 ) ( 1 - 0.85 ) = 0.9625$, 뒤는 $1 - ( 1 - 0.80 ) ( 1 - 0.90 ) = 0.98$이다. 전체는 $0.80 \times 0.90 \times 0.9625 \times 0.98 \times 0.85 \fallingdotseq 0.578$이다.</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
-          <t>① 0.378 은 계산과 맞지 않는다.&lt;br&gt;② 0.478 도 맞지 않는다.&lt;br&gt;④ 0.675 도 맞지 않는다.</t>
+          <t>① 0.378은 계산과 맞지 않는다.&lt;br&gt;② 0.478 도 맞지 않는다.&lt;br&gt;④ 0.675 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;직렬·병렬 결합의 신뢰도&lt;/strong&gt;&lt;br&gt;병렬 두 곳을 먼저 &lt;strong&gt;0.9625 와 0.98&lt;/strong&gt;로 바꿔 놓으면 &lt;strong&gt;직렬 다섯 개의 곱&lt;/strong&gt;이 된다. &lt;strong&gt;병렬 값은 늘 그 안의 가장 큰 값보다 크다&lt;/strong&gt;는 점으로 계산을 검산할 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;병렬을 먼저 하나의 수로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;직렬·병렬 결합의 신뢰도&lt;/strong&gt;&lt;br&gt;병렬 두 곳을 먼저 &lt;strong&gt;0.9625와 0.98&lt;/strong&gt;로 바꿔 놓으면 &lt;strong&gt;직렬 다섯 개의 곱&lt;/strong&gt;이 된다. &lt;strong&gt;병렬 값은 늘 그 안의 가장 큰 값보다 크다&lt;/strong&gt;는 점으로 계산을 검산할 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;병렬을 먼저 하나의 수로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5488,7 @@
       </c>
       <c r="AI34" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;기초대사량(BMR)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;RMR = 작업대사량 ÷ 기초대사량&lt;/strong&gt;이 실무에서 쓰인다. &lt;strong&gt;기초대사량이 분모&lt;/strong&gt;이므로, 같은 일이라도 &lt;strong&gt;몸집이 큰 사람은 RMR 이 낮게&lt;/strong&gt; 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;목숨을 잇는 데만 드는 것이 기초대사량&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;기초대사량(BMR)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;RMR = 작업대사량 ÷ 기초대사량&lt;/strong&gt;이 실무에서 쓰인다. &lt;strong&gt;기초대사량이 분모&lt;/strong&gt;이므로, 같은 일이라도 &lt;strong&gt;몸집이 큰 사람은 RMR이 낮게&lt;/strong&gt; 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;목숨을 잇는 데만 드는 것이 기초대사량&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5607,7 @@
       </c>
       <c r="AG35" s="32" t="inlineStr">
         <is>
-          <t>키보드·마우스 조작은 &lt;strong&gt;하루 4시간 이상&lt;/strong&gt; 이라야 부담작업이다. 2시간이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;근골격계부담작업 11가지 — 시간 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;시간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;작업&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4시간 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제1호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;키보드·마우스 조작&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2시간 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제2 ~ 제7호&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 동작 반복 · 팔을 머리 위로 · 목이나 허리를 굽힘 · 쪼그려 앉기 · 손가락으로 집기 · 손으로 두드리기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10회 이상/일&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제8호&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25 [kg] 이상&lt;/u&gt; 물체 들기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;25회 이상/일&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제9호&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [kg] 이상&lt;/u&gt; 물체를 무릎 아래·어깨 위에서 들기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2시간 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제10호&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4.5 [kg] 이상&lt;/u&gt; 물건을 한 손으로 들거나 쥐기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2시간 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제11호&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;충격을 가하는 작업&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>키보드·마우스 조작은 &lt;strong&gt;하루 4시간 이상&lt;/strong&gt;이라야 부담작업이다. 2시간이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;근골격계부담작업 11가지 — 시간 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;시간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;작업&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4시간 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제1호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;키보드·마우스 조작&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2시간 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제2 ~ 제7호&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 동작 반복 · 팔을 머리 위로 · 목이나 허리를 굽힘 · 쪼그려 앉기 · 손가락으로 집기 · 손으로 두드리기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10회 이상/일&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제8호&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25 [kg] 이상&lt;/u&gt; 물체 들기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;25회 이상/일&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제9호&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [kg] 이상&lt;/u&gt; 물체를 무릎 아래·어깨 위에서 들기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2시간 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제10호&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4.5 [kg] 이상&lt;/u&gt; 물건을 한 손으로 들거나 쥐기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2시간 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제11호&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;충격을 가하는 작업&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH35" s="32" t="inlineStr">
@@ -5613,7 +5617,7 @@
       </c>
       <c r="AI35" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;근골격계부담작업의 범위 (고용노동부 고시)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;시간 기준이 4시간인 것은 제1호(키보드·마우스) 하나뿐&lt;/strong&gt;이고 나머지는 모두 2시간이다. &lt;strong&gt;2 로 바꿔 놓는 것&lt;/strong&gt;이 이 유형의 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;키보드만 4시간, 나머지는 2시간&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;근골격계부담작업의 범위 (고용노동부 고시)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;시간 기준이 4시간인 것은 제1호(키보드·마우스) 하나뿐&lt;/strong&gt;이고 나머지는 모두 2시간이다. &lt;strong&gt;2로 바꿔 놓는 것&lt;/strong&gt;이 이 유형의 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;키보드만 4시간, 나머지는 2시간&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5865,17 +5869,17 @@
       </c>
       <c r="AG37" s="32" t="inlineStr">
         <is>
-          <t>$T = H ( X ) + H ( Y ) - H ( X {,} Y )$ 다. 자극 A 50 · B 50 이므로 $H ( X ) = 1.0$, 반응 1 이 60 · 2 가 40 이므로 $H ( Y ) \fallingdotseq 0.971$, 세 칸(50 · 10 · 40)에서 $H ( X {,} Y ) \fallingdotseq 1.361$ 이다. 따라서 $T = 1.0 + 0.971 - 1.361 = 0.610$ 이다.</t>
+          <t>$T = H ( X ) + H ( Y ) - H ( X {,} Y )$다. 자극 A 50 · B 50이므로 $H ( X ) = 1.0$, 반응 1이 60 · 2가 40이므로 $H ( Y ) \fallingdotseq 0.971$, 세 칸(50 · 10 · 40)에서 $H ( X {,} Y ) \fallingdotseq 1.361$이다. 따라서 $T = 1.0 + 0.971 - 1.361 = 0.610$이다.</t>
         </is>
       </c>
       <c r="AH37" s="32" t="inlineStr">
         <is>
-          <t>② 0.871 은 계산과 맞지 않는다.&lt;br&gt;③ 1.000 은 자극의 엔트로피 $H ( X )$ 값이다.&lt;br&gt;④ 1.361 은 결합 엔트로피 $H ( X {,} Y )$ 값이다.</t>
+          <t>② 0.871은 계산과 맞지 않는다.&lt;br&gt;③ 1.000은 자극의 엔트로피 $H ( X )$ 값이다.&lt;br&gt;④ 1.361은 결합 엔트로피 $H ( X {,} Y )$ 값이다.</t>
         </is>
       </c>
       <c r="AI37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전달정보량 $T ( X ; Y )$&lt;/strong&gt;&lt;br&gt;$H = \sum p_{i} \log_{2} ( 1 / p_{i} )$ 이다. &lt;strong&gt;보낸 정보와 받은 정보를 더한 뒤 둘을 합친 것을 빼면 겹치는 부분&lt;/strong&gt;이 남는데, 그것이 &lt;strong&gt;제대로 전달된 양&lt;/strong&gt;이다. 오류가 없으면 $T = H ( X )$ 가 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $T = H ( X ) + H ( Y ) - H ( X {,} Y )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전달정보량 $T ( X ; Y )$&lt;/strong&gt;&lt;br&gt;$H = \sum p_{i} \log_{2} ( 1 / p_{i} )$이다. &lt;strong&gt;보낸 정보와 받은 정보를 더한 뒤 둘을 합친 것을 빼면 겹치는 부분&lt;/strong&gt;이 남는데, 그것이 &lt;strong&gt;제대로 전달된 양&lt;/strong&gt;이다. 오류가 없으면 $T = H ( X )$가 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $T = H ( X ) + H ( Y ) - H ( X {,} Y )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6137,7 @@
       </c>
       <c r="AI39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시각적 부호의 유형&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;묘사적은 보면 알고, 추상적은 짐작할 수 있고, 임의적은 배워야 안다&lt;/strong&gt;. &lt;strong&gt;해골 그림이 「독」을 뜻한다는 것은 약속&lt;/strong&gt; 일 뿐 그림 자체에서 나오지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;묘사 · 추상 · 임의&lt;/u&gt; 셋뿐.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;시각적 부호의 유형&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;묘사적은 보면 알고, 추상적은 짐작할 수 있고, 임의적은 배워야 안다&lt;/strong&gt;. &lt;strong&gt;해골 그림이 「독」을 뜻한다는 것은 약속&lt;/strong&gt;일 뿐 그림 자체에서 나오지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;묘사 · 추상 · 임의&lt;/u&gt; 셋뿐.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6266,7 @@
       </c>
       <c r="AI40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;명료도 지수(articulation index)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「가중치를 곱해 합계」&lt;/strong&gt;라는 말이 명료도 지수를 가리킨다. &lt;strong&gt;PSIL 은 그냥 평균&lt;/strong&gt;이라 가중치가 없다. 이 한 낱말로 둘이 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가중치를 곱해 더하면 명료도 지수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;명료도 지수(articulation index)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「가중치를 곱해 합계」&lt;/strong&gt;라는 말이 명료도 지수를 가리킨다. &lt;strong&gt;PSIL은 그냥 평균&lt;/strong&gt;이라 가중치가 없다. 이 한 낱말로 둘이 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가중치를 곱해 더하면 명료도 지수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6381,17 +6385,17 @@
       </c>
       <c r="AG41" s="32" t="inlineStr">
         <is>
-          <t>조도는 &lt;strong&gt;거리의 제곱에 반비례&lt;/strong&gt; 한다. $E_{2} = 120 \times ( \dfrac{5}{2} )^{2} = 120 \times 6.25 = 750$ [lux] 다.</t>
+          <t>조도는 &lt;strong&gt;거리의 제곱에 반비례&lt;/strong&gt;한다. $E_{2} = 120 \times ( \dfrac{5}{2} )^{2} = 120 \times 6.25 = 750$ [lux]다.</t>
         </is>
       </c>
       <c r="AH41" s="32" t="inlineStr">
         <is>
-          <t>① 150 [lux] 는 계산과 맞지 않는다.&lt;br&gt;② 192.2 [lux] 도 맞지 않는다.&lt;br&gt;④ 3,000 [lux] 는 거리를 제곱하지 않고 잘못 곱한 값이다.</t>
+          <t>① 150 [lux]는 계산과 맞지 않는다.&lt;br&gt;② 192.2 [lux] 도 맞지 않는다.&lt;br&gt;④ 3,000 [lux]는 거리를 제곱하지 않고 잘못 곱한 값이다.</t>
         </is>
       </c>
       <c r="AI41" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;조도와 거리의 관계&lt;/strong&gt;&lt;br&gt;$\text{조도} = \dfrac{\text{광도}}{\text{거리}}^{2}$ 다. &lt;strong&gt;가까워지면 밝아지고, 그 배수는 거리비의 제곱&lt;/strong&gt;이다. 5 → 2 로 &lt;strong&gt;2.5배 가까워졌으니 6.25배 밝아진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;조도는 거리 제곱에 반비례&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;조도와 거리의 관계&lt;/strong&gt;&lt;br&gt;$\text{조도} = \dfrac{\text{광도}}{\text{거리}}^{2}$다. &lt;strong&gt;가까워지면 밝아지고, 그 배수는 거리비의 제곱&lt;/strong&gt;이다. 5 → 2로 &lt;strong&gt;2.5배 가까워졌으니 6.25배 밝아진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;조도는 거리 제곱에 반비례&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6524,7 @@
       </c>
       <c r="AI42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;작업부하의 생리적 측정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;몸을 쓰면 산소와 심장, 머리를 쓰면 눈과 뇌&lt;/strong&gt;를 본다. &lt;strong&gt;점멸융합주파수는 눈이 깜박임을 하나로 느끼기 시작하는 주파수&lt;/strong&gt;로, 피로하면 낮아진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;CFF 는 정신적 피로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;작업부하의 생리적 측정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;몸을 쓰면 산소와 심장, 머리를 쓰면 눈과 뇌&lt;/strong&gt;를 본다. &lt;strong&gt;점멸융합주파수는 눈이 깜박임을 하나로 느끼기 시작하는 주파수&lt;/strong&gt;로, 피로하면 낮아진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;CFF는 정신적 피로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7155,17 +7159,17 @@
       </c>
       <c r="AG47" s="32" t="inlineStr">
         <is>
-          <t>$\text{허용응력} = \dfrac{\text{인장강도}}{\text{안전율}} = \dfrac{350}{4} = 87.5$ [N/㎟] 다. &lt;strong&gt;1 [MPa] = 1 [N/㎟]&lt;/strong&gt;이므로 단위를 바꿀 필요가 없다.</t>
+          <t>$\text{허용응력} = \dfrac{\text{인장강도}}{\text{안전율}} = \dfrac{350}{4} = 87.5$ [N/㎟]다. &lt;strong&gt;1 [MPa] = 1 [N/㎟]&lt;/strong&gt;이므로 단위를 바꿀 필요가 없다.</t>
         </is>
       </c>
       <c r="AH47" s="32" t="inlineStr">
         <is>
-          <t>① 76.4 는 계산과 맞지 않는다.&lt;br&gt;③ 98.7 도 맞지 않는다.&lt;br&gt;④ 102.3 도 맞지 않는다.</t>
+          <t>① 76.4는 계산과 맞지 않는다.&lt;br&gt;③ 98.7 도 맞지 않는다.&lt;br&gt;④ 102.3 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI47" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전율과 허용응력&lt;/strong&gt;&lt;br&gt;$\text{안전율} = \dfrac{\text{기준강도}}{\text{허용응력}}$ 다. &lt;strong&gt;연성 재료는 항복점, 취성 재료는 극한강도&lt;/strong&gt;를 기준강도로 삼는다. &lt;strong&gt;1 [MPa] = 1 [N/㎟]&lt;/strong&gt;라는 환산은 자주 쓰이니 외워 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;허용응력 = 인장강도 ÷ 안전율&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전율과 허용응력&lt;/strong&gt;&lt;br&gt;$\text{안전율} = \dfrac{\text{기준강도}}{\text{허용응력}}$다. &lt;strong&gt;연성 재료는 항복점, 취성 재료는 극한강도&lt;/strong&gt;를 기준강도로 삼는다. &lt;strong&gt;1 [MPa] = 1 [N/㎟]&lt;/strong&gt;라는 환산은 자주 쓰이니 외워 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;허용응력 = 인장강도 ÷ 안전율&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7417,7 @@
       </c>
       <c r="AG49" s="32" t="inlineStr">
         <is>
-          <t>전면 칩 가드의 폭은 &lt;strong&gt;새들 폭 이상&lt;/strong&gt; 이라야 한다. 이하로 하면 &lt;strong&gt;칩이 옆으로 새어 나온다&lt;/strong&gt;.</t>
+          <t>전면 칩 가드의 폭은 &lt;strong&gt;새들 폭 이상&lt;/strong&gt;이라야 한다. 이하로 하면 &lt;strong&gt;칩이 옆으로 새어 나온다&lt;/strong&gt;.</t>
         </is>
       </c>
       <c r="AH49" s="32" t="inlineStr">
@@ -8187,17 +8191,17 @@
       </c>
       <c r="AG55" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;하나는 최고사용압력 이하, 다른 하나는 최고사용압력의 1.05배 이하&lt;/strong&gt;로 맞춘다. 1 [MPa] 이면 &lt;strong&gt;1 [MPa] 과 1.05 [MPa]&lt;/strong&gt;이다.</t>
+          <t>&lt;strong&gt;하나는 최고사용압력 이하, 다른 하나는 최고사용압력의 1.05배 이하&lt;/strong&gt;로 맞춘다. 1 [MPa] 이면 &lt;strong&gt;1 [MPa]과 1.05 [MPa]&lt;/strong&gt;이다.</t>
         </is>
       </c>
       <c r="AH55" s="32" t="inlineStr">
         <is>
-          <t>① 둘 다 1.1 [MPa] 이면 하나도 최고사용압력 이하가 아니다.&lt;br&gt;② 1.1 [MPa] 은 1.05배를 넘는다.&lt;br&gt;④ 둘 다 1.05 [MPa] 이면 최고사용압력 이하인 것이 없다.</t>
+          <t>① 둘 다 1.1 [MPa] 이면 하나도 최고사용압력 이하가 아니다.&lt;br&gt;② 1.1 [MPa]은 1.05배를 넘는다.&lt;br&gt;④ 둘 다 1.05 [MPa] 이면 최고사용압력 이하인 것이 없다.</t>
         </is>
       </c>
       <c r="AI55" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제116조 — 압력방출장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하나는 정상 압력에서 먼저 열고, 다른 하나는 조금 높은 압력에서 예비로 연다&lt;/strong&gt;. 이 두 단계 얼개를 알면 숫자를 외우지 않아도 보기가 갈린다. &lt;strong&gt;1년에 1회 이상 검사&lt;/strong&gt; 하고 봉인해 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하나는 최고사용압력, 하나는 1.05배&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C116%EC%A1%B0" target="_blank"&gt;제116조(압력방출장치)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ ① 사업주는 보일러의 안전한 가동을 위하여 보일러 규격에 맞는 압력방출장치를 1개 또는 2개 이상 설치하고 최고사용압력(설계압력 또는 최고허용압력을 말한다. 이하 같다) 이하에서 작동되도록 하여야 한다. 다만, 압력방출장치가 2개 이상 설치된 경우에는 최고사용압력 이하에서 1개가 작동되고, 다른 압력방출장치는 최고사용압력 &lt;strong&gt;1.05배 이하&lt;/strong&gt;에서 작동되도록 부착하여야 한다.&lt;br&gt;② 제1항의 압력방출장치는 매년 1회 이상 「국가표준기본법」 제14조제3항에 따라 산업통상부장관의 지정을 받은 국가교정업무 전담기관(이하 "국가교정기관"이라 한다)에서 교정을 받은 압력계를 이용하여 설정압력에서 압력방출장치가 적정하게 작동하는지를 검사한 후 납으로 봉인하여 사용하여야 한다. 다만, 영 제43조에 따른 공정안전보고서 제출 대상으로서 고용노동부장관이 실시하는 공정안전보고서 이행상태 평가결과가 우수한 사업장은 압력방출장치에 대하여 4년마다 1회 이상 설정압력에서 압력방출장치가 적정하게 작동하는지를 검사할 수 있다. &amp;lt;개정 2013.3.23, 2019.12.26, 2025.10.1&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제116조 — 압력방출장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하나는 정상 압력에서 먼저 열고, 다른 하나는 조금 높은 압력에서 예비로 연다&lt;/strong&gt;. 이 두 단계 얼개를 알면 숫자를 외우지 않아도 보기가 갈린다. &lt;strong&gt;1년에 1회 이상 검사&lt;/strong&gt;하고 봉인해 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하나는 최고사용압력, 하나는 1.05배&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C116%EC%A1%B0" target="_blank"&gt;제116조(압력방출장치)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ ① 사업주는 보일러의 안전한 가동을 위하여 보일러 규격에 맞는 압력방출장치를 1개 또는 2개 이상 설치하고 최고사용압력(설계압력 또는 최고허용압력을 말한다. 이하 같다) 이하에서 작동되도록 하여야 한다. 다만, 압력방출장치가 2개 이상 설치된 경우에는 최고사용압력 이하에서 1개가 작동되고, 다른 압력방출장치는 최고사용압력 &lt;strong&gt;1.05배 이하&lt;/strong&gt;에서 작동되도록 부착하여야 한다.&lt;br&gt;② 제1항의 압력방출장치는 매년 1회 이상 「국가표준기본법」 제14조제3항에 따라 산업통상부장관의 지정을 받은 국가교정업무 전담기관(이하 "국가교정기관"이라 한다)에서 교정을 받은 압력계를 이용하여 설정압력에서 압력방출장치가 적정하게 작동하는지를 검사한 후 납으로 봉인하여 사용하여야 한다. 다만, 영 제43조에 따른 공정안전보고서 제출 대상으로서 고용노동부장관이 실시하는 공정안전보고서 이행상태 평가결과가 우수한 사업장은 압력방출장치에 대하여 4년마다 1회 이상 설정압력에서 압력방출장치가 적정하게 작동하는지를 검사할 수 있다. &amp;lt;개정 2013.3.23, 2019.12.26, 2025.10.1&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8325,7 @@
       </c>
       <c r="AH56" s="32" t="inlineStr">
         <is>
-          <t>② 2.1 [m] 라는 기준은 없다.&lt;br&gt;③ 2.4 [m] 도 아니다.&lt;br&gt;④ 2.7 [m] 도 아니다.</t>
+          <t>② 2.1 [m]라는 기준은 없다.&lt;br&gt;③ 2.4 [m] 도 아니다.&lt;br&gt;④ 2.7 [m] 도 아니다.</t>
         </is>
       </c>
       <c r="AI56" s="32" t="inlineStr">
@@ -8707,17 +8711,17 @@
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>동하중은 $W_{d} = \dfrac{W_{s}}{g} \times a = \dfrac{2 {,} 000}{9.8} \times 20 \fallingdotseq 4 {,} 081.6$ [kgf] 다. 총하중은 $2 {,} 000 + 4 {,} 081.6 = 6 {,} 081.6$ [kgf] 이고, $\times 9.8 = 59 {,} 600$ [N] 이므로 약 &lt;strong&gt;59.6 [kN]&lt;/strong&gt;이다.</t>
+          <t>동하중은 $W_{d} = \dfrac{W_{s}}{g} \times a = \dfrac{2 {,} 000}{9.8} \times 20 \fallingdotseq 4 {,} 081.6$ [kgf]다. 총하중은 $2 {,} 000 + 4 {,} 081.6 = 6 {,} 081.6$ [kgf]이고, $\times 9.8 = 59 {,} 600$ [N]이므로 약 &lt;strong&gt;59.6 [kN]&lt;/strong&gt;이다.</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
-          <t>① 42.8 [kN] 은 계산과 맞지 않는다.&lt;br&gt;③ 74.5 [kN] 도 맞지 않는다.&lt;br&gt;④ 91.3 [kN] 도 맞지 않는다.</t>
+          <t>① 42.8 [kN]은 계산과 맞지 않는다.&lt;br&gt;③ 74.5 [kN] 도 맞지 않는다.&lt;br&gt;④ 91.3 [kN] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI59" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;총하중 = 정하중 + 동하중&lt;/strong&gt;&lt;br&gt;$W = W_{s} ( 1 + \dfrac{a}{g} )$ 로 한 번에 풀 수도 있다 — $2 {,} 000 \times ( 1 + 20 / 9.8 ) = 6 {,} 082$ [kgf]. &lt;strong&gt;가속도가 중력가속도의 두 배쯤이니 하중도 세 배쯤&lt;/strong&gt;이라는 어림으로 검산된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $W = W_{s} ( 1 + a / g )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;총하중 = 정하중 + 동하중&lt;/strong&gt;&lt;br&gt;$W = W_{s} ( 1 + \dfrac{a}{g} )$로 한 번에 풀 수도 있다 — $2 {,} 000 \times ( 1 + 20 / 9.8 ) = 6 {,} 082$ [kgf]. &lt;strong&gt;가속도가 중력가속도의 두 배쯤이니 하중도 세 배쯤&lt;/strong&gt;이라는 어림으로 검산된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $W = W_{s} ( 1 + a / g )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8965,17 +8969,17 @@
       </c>
       <c r="AG61" s="32" t="inlineStr">
         <is>
-          <t>표면속도는 $V = \dfrac{\pi D N}{1 {,} 000} = \dfrac{\pi \times 300 \times 30}{1 {,} 000} \fallingdotseq 28.3$ [m/min] 로 &lt;strong&gt;30 [m/min] 미만&lt;/strong&gt;이다. 따라서 급정지거리는 &lt;strong&gt;원주의 1/3&lt;/strong&gt; 이내이므로 $\pi \times 300 \times \dfrac{1}{3} \fallingdotseq 314$ [mm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;롤러기의 급정지거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;앞면 롤러의 표면속도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;급정지거리&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/min] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;앞면 롤러 원주의 1/3 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/min] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;앞면 롤러 원주의 1/2.5 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>표면속도는 $V = \dfrac{\pi D N}{1 {,} 000} = \dfrac{\pi \times 300 \times 30}{1 {,} 000} \fallingdotseq 28.3$ [m/min]로 &lt;strong&gt;30 [m/min] 미만&lt;/strong&gt;이다. 따라서 급정지거리는 &lt;strong&gt;원주의 1/3&lt;/strong&gt; 이내이므로 $\pi \times 300 \times \dfrac{1}{3} \fallingdotseq 314$ [mm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;롤러기의 급정지거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;앞면 롤러의 표면속도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;급정지거리&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/min] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;앞면 롤러 원주의 1/3 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/min] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;앞면 롤러 원주의 1/2.5 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH61" s="32" t="inlineStr">
         <is>
-          <t>① 37.7 [mm] 는 자릿수가 맞지 않는다.&lt;br&gt;② 31.4 [mm] 도 자릿수가 맞지 않는다.&lt;br&gt;③ 377 [mm] 는 1/2.5 를 적용한 값이다.</t>
+          <t>① 37.7 [mm]는 자릿수가 맞지 않는다.&lt;br&gt;② 31.4 [mm] 도 자릿수가 맞지 않는다.&lt;br&gt;③ 377 [mm]는 1/2.5를 적용한 값이다.</t>
         </is>
       </c>
       <c r="AI61" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방호장치 안전인증 고시 — 롤러기 급정지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;먼저 표면속도를 구해 30 [m/min] 을 넘는지 보고&lt;/strong&gt; 나서 1/3 이냐 1/2.5 냐를 정한다. 순서를 건너뛰고 곧바로 나누면 377 을 골라 틀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 [m/min] 미만이면 1/3&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방호장치 안전인증 고시 — 롤러기 급정지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;먼저 표면속도를 구해 30 [m/min]을 넘는지 보고&lt;/strong&gt; 나서 1/3 이냐 1/2.5 냐를 정한다. 순서를 건너뛰고 곧바로 나누면 377을 골라 틀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 [m/min] 미만이면 1/3&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9237,7 @@
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;퓨즈의 기능&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;퓨즈는 「많이 흐르면」 끊고, 누전차단기는 「새면」 끊는다&lt;/strong&gt;. 두 장치는 서로 대신하지 못하므로 &lt;strong&gt;함께 설치&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;퓨즈는 과전류&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;퓨즈의 기능&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;퓨즈는 「많이 흐르면」 끊고, 누전차단기는 「새면」 끊는다&lt;/strong&gt;. 두 장치는 서로 대신하지 못하므로 &lt;strong&gt;함께 설치&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;퓨즈는 과전류&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9485,7 @@
       </c>
       <c r="AG65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;대지전압 150 [V] 를 넘는&lt;/strong&gt; 이동형·휴대형 전기기계기구에는 누전차단기를 달아야 한다. 220 [V] 는 여기에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전차단기를 설치하지 않아도 되는 경우&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;면제 사유&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2중 절연구조의 기계기구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;절연이 두 겹이라 감전 우려가 없다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연대 위에서 사용하는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대지와 끊어져 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비접지방식의 전로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;돌아갈 길이 없다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전원측에 절연변압기(2차 300 [V] 이하)를 시설한 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원이 대지와 끊어져 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;대지전압 150 [V]를 넘는&lt;/strong&gt; 이동형·휴대형 전기기계기구에는 누전차단기를 달아야 한다. 220 [V]는 여기에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전차단기를 설치하지 않아도 되는 경우&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;면제 사유&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2중 절연구조의 기계기구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;절연이 두 겹이라 감전 우려가 없다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절연대 위에서 사용하는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대지와 끊어져 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비접지방식의 전로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;돌아갈 길이 없다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전원측에 절연변압기(2차 300 [V] 이하)를 시설한 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원이 대지와 끊어져 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH65" s="32" t="inlineStr">
@@ -9744,7 +9748,7 @@
       </c>
       <c r="AH67" s="32" t="inlineStr">
         <is>
-          <t>② 35 ~ 50 [V] 는 기준보다 높다.&lt;br&gt;③ 55 ~ 75 [V] 는 오히려 무부하전압의 범위에 가깝다.&lt;br&gt;④ 80 ~ 100 [V] 도 기준을 크게 넘는다.</t>
+          <t>② 35 ~ 50 [V]는 기준보다 높다.&lt;br&gt;③ 55 ~ 75 [V]는 오히려 무부하전압의 범위에 가깝다.&lt;br&gt;④ 80 ~ 100 [V] 도 기준을 크게 넘는다.</t>
         </is>
       </c>
       <c r="AI67" s="32" t="inlineStr">
@@ -9868,7 +9872,7 @@
       </c>
       <c r="AG68" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;관계자 외에도 쉽게 드나들 수 있는 곳&lt;/strong&gt;에 충전부를 두는 것은 감전 위험을 키운다. 조문은 &lt;strong&gt;충전부를 관계자 외 출입금지 장소에 설치&lt;/strong&gt; 하도록 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;직접 접촉에 의한 감전방지 (규칙 제301조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충전부가 노출되지 않도록 폐쇄형 외함구조로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충전부에 충분한 절연효과가 있는 방호망이나 절연덮개를 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충전부는 내구성이 있는 절연물로 완전히 덮어 감쌀 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발전소·변전소 등 관계자 외 출입금지 장소에 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「출입이 가능한」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전주 위·철탑 위 등 사람이 접촉할 우려가 없는 곳에 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;관계자 외에도 쉽게 드나들 수 있는 곳&lt;/strong&gt;에 충전부를 두는 것은 감전 위험을 키운다. 조문은 &lt;strong&gt;충전부를 관계자 외 출입금지 장소에 설치&lt;/strong&gt;하도록 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;직접 접촉에 의한 감전방지 (규칙 제301조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충전부가 노출되지 않도록 폐쇄형 외함구조로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충전부에 충분한 절연효과가 있는 방호망이나 절연덮개를 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충전부는 내구성이 있는 절연물로 완전히 덮어 감쌀 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발전소·변전소 등 관계자 외 출입금지 장소에 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「출입이 가능한」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전주 위·철탑 위 등 사람이 접촉할 우려가 없는 곳에 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH68" s="32" t="inlineStr">
@@ -9980,7 +9984,7 @@
       <c r="AC69" s="32" t="inlineStr"/>
       <c r="AD69" s="32" t="inlineStr">
         <is>
-          <t>산소 함유율 21 %v/v 의 공기</t>
+          <t>산소 함유율 21 %v/v의 공기</t>
         </is>
       </c>
       <c r="AE69" s="32" t="inlineStr"/>
@@ -9989,17 +9993,17 @@
       </c>
       <c r="AG69" s="32" t="inlineStr">
         <is>
-          <t>상대습도는 &lt;strong&gt;45 ~ 85 [%]&lt;/strong&gt;다. 40 ~ 80 [%] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭기기의 표준환경조건&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;80 ~ 110 [kPa]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상대습도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;45 ~ 85 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 ~ 80 [%] 이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주위온도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−20 ~ 40 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소 함유율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;21 [%v/v] 의 공기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>상대습도는 &lt;strong&gt;45 ~ 85 [%]&lt;/strong&gt;다. 40 ~ 80 [%]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭기기의 표준환경조건&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;80 ~ 110 [kPa]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상대습도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;45 ~ 85 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 ~ 80 [%]이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주위온도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−20 ~ 40 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소 함유율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;21 [%v/v]의 공기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH69" s="32" t="inlineStr">
         <is>
-          <t>① 압력 80 ~ 110 [kPa] 는 맞다.&lt;br&gt;③ 주위온도 −20 ~ 40 [℃] 도 맞다.&lt;br&gt;④ 산소 함유율 21 [%v/v] 의 공기도 맞다.</t>
+          <t>① 압력 80 ~ 110 [kPa]는 맞다.&lt;br&gt;③ 주위온도 −20 ~ 40 [℃] 도 맞다.&lt;br&gt;④ 산소 함유율 21 [%v/v]의 공기도 맞다.</t>
         </is>
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;KS C IEC 60079-0 — 방폭기기의 표준환경조건&lt;/strong&gt;&lt;br&gt;네 항목 가운데 &lt;strong&gt;습도만 45 ~ 85&lt;/strong&gt;로 다른 셋과 어긋난 숫자를 쓴다. 보기는 &lt;strong&gt;앞뒤로 5씩 옮겨 40 ~ 80 으로&lt;/strong&gt; 바꿔 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;습도만 45 ~ 85 [%]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;KS C IEC 60079-0 — 방폭기기의 표준환경조건&lt;/strong&gt;&lt;br&gt;네 항목 가운데 &lt;strong&gt;습도만 45 ~ 85&lt;/strong&gt;로 다른 셋과 어긋난 숫자를 쓴다. 보기는 &lt;strong&gt;앞뒤로 5씩 옮겨 40 ~ 80으로&lt;/strong&gt; 바꿔 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;습도만 45 ~ 85 [%]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10768,12 +10772,12 @@
       </c>
       <c r="AH75" s="32" t="inlineStr">
         <is>
-          <t>① 40 [A/㎟] 는 인화단계다.&lt;br&gt;③ 65 [A/㎟] 는 발화단계다.&lt;br&gt;④ 120 [A/㎟] 는 순간용단 단계다.</t>
+          <t>① 40 [A/㎟]는 인화단계다.&lt;br&gt;③ 65 [A/㎟]는 발화단계다.&lt;br&gt;④ 120 [A/㎟]는 순간용단 단계다.</t>
         </is>
       </c>
       <c r="AI75" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;절연전선의 과전류 연소단계&lt;/strong&gt;&lt;br&gt;네 경계값이 &lt;strong&gt;40 · 43 · 60 · 120&lt;/strong&gt;이다. 각 보기가 &lt;strong&gt;한 단계씩 정확히 대응&lt;/strong&gt; 하도록 짜여 있으므로, 경계값만 잡아 두면 어느 단계를 물어도 풀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;40 · 43 · 60 · 120&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;절연전선의 과전류 연소단계&lt;/strong&gt;&lt;br&gt;네 경계값이 &lt;strong&gt;40 · 43 · 60 · 120&lt;/strong&gt;이다. 각 보기가 &lt;strong&gt;한 단계씩 정확히 대응&lt;/strong&gt;하도록 짜여 있으므로, 경계값만 잡아 두면 어느 단계를 물어도 풀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;40 · 43 · 60 · 120&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11283,7 @@
       </c>
       <c r="AG79" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;단락 접지기구의 철거&lt;/strong&gt;는 &lt;strong&gt;작업이 끝난 뒤&lt;/strong&gt;의 일이다. 작업 전에는 오히려 &lt;strong&gt;설치&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전작업의 세 때&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;때&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;하는 일&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전로 개로 → 개폐기 잠금·표시 → 잔류전하 방전 → 검전기로 정전 확인 → 단락접지기구 설치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개폐기 관리 · 단락접지 상태 수시 확인 · 근접 활선에 대한 방호&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단락접지기구 철거 → 사람 이탈 확인 → 잠금·표시 제거 → 통전&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;단락 접지기구의 철거&lt;/strong&gt;는 &lt;strong&gt;작업이 끝난 뒤&lt;/strong&gt;의 일이다. 작업 전에는 오히려 &lt;strong&gt;설치&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전작업의 세 때&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;때&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;하는 일&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전로 개로 → 개폐기 잠금·표시 → 잔류전하 방전 → 검전기로 정전 확인 → 단락접지기구 설치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개폐기 관리 · 단락접지 상태 수시 확인 · 근접 활선에 대한 방호&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단락접지기구 철거 → 사람 이탈 확인 → 잠금·표시 제거 → 통전&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH79" s="32" t="inlineStr">
@@ -11418,7 +11422,7 @@
       </c>
       <c r="AI80" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 — 정전작업 중의 조치&lt;/strong&gt;&lt;br&gt;77번과 짝이다. 작업 중에 하는 일은 &lt;strong&gt;상태를 지키는 것&lt;/strong&gt; 뿐이다 — &lt;strong&gt;개폐기를 남이 못 올리게 관리하고 · 단락접지 상태를 살피고 · 근접 활선을 방호한다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업 중에는 상태를 지킨다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 — 정전작업 중의 조치&lt;/strong&gt;&lt;br&gt;77번과 짝이다. 작업 중에 하는 일은 &lt;strong&gt;상태를 지키는 것&lt;/strong&gt;뿐이다 — &lt;strong&gt;개폐기를 남이 못 올리게 관리하고 · 단락접지 상태를 살피고 · 근접 활선을 방호한다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업 중에는 상태를 지킨다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11795,7 +11799,7 @@
       </c>
       <c r="AG83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아세톤&lt;/strong&gt;이다. 아세틸렌은 압축하면 &lt;strong&gt;분해폭발&lt;/strong&gt; 하므로 &lt;strong&gt;다공성 물질에 스민 아세톤에 녹여&lt;/strong&gt; 담는다.</t>
+          <t>&lt;strong&gt;아세톤&lt;/strong&gt;이다. 아세틸렌은 압축하면 &lt;strong&gt;분해폭발&lt;/strong&gt;하므로 &lt;strong&gt;다공성 물질에 스민 아세톤에 녹여&lt;/strong&gt; 담는다.</t>
         </is>
       </c>
       <c r="AH83" s="32" t="inlineStr">
@@ -11805,7 +11809,7 @@
       </c>
       <c r="AI83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아세틸렌의 용해 저장&lt;/strong&gt;&lt;br&gt;아세톤 1 [L] 에 아세틸렌이 &lt;strong&gt;약 25 [L]&lt;/strong&gt; 녹는다. 용기를 &lt;strong&gt;반드시 세워 두는&lt;/strong&gt; 까닭은 눕히면 &lt;strong&gt;아세톤이 함께 흘러나오기&lt;/strong&gt; 때문이다. &lt;strong&gt;아세틸렌 압력은 1.5 [kgf/㎠] 이하&lt;/strong&gt;로 제한한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세톤에 녹여 다공질에 담는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;아세틸렌의 용해 저장&lt;/strong&gt;&lt;br&gt;아세톤 1 [L]에 아세틸렌이 &lt;strong&gt;약 25 [L]&lt;/strong&gt; 녹는다. 용기를 &lt;strong&gt;반드시 세워 두는&lt;/strong&gt; 까닭은 눕히면 &lt;strong&gt;아세톤이 함께 흘러나오기&lt;/strong&gt; 때문이다. &lt;strong&gt;아세틸렌 압력은 1.5 [kgf/㎠] 이하&lt;/strong&gt;로 제한한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세톤에 녹여 다공질에 담는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11916,17 +11920,17 @@
       </c>
       <c r="AG84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;수소&lt;/strong&gt;다. 분자량 2 로 &lt;strong&gt;모든 기체 가운데 가장 가볍다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;보기 기체의 분자량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기체&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;분자량&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;공기(29)와 견주면&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소 H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;14배 가볍다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세틸렌 C₂H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;26&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조금 가볍다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에틸렌 C₂H₄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;28&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;거의 같다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부탄 C₄H₁₀&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;58&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2배 무겁다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;수소&lt;/strong&gt;다. 분자량 2로 &lt;strong&gt;모든 기체 가운데 가장 가볍다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;보기 기체의 분자량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기체&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;분자량&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;공기(29)와 견주면&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소 H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;14배 가볍다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세틸렌 C₂H₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;26&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조금 가볍다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에틸렌 C₂H₄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;28&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;거의 같다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부탄 C₄H₁₀&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;58&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2배 무겁다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH84" s="32" t="inlineStr">
         <is>
-          <t>① 아세틸렌은 분자량 26 이다.&lt;br&gt;③ 부탄은 58 로 가장 무겁다.&lt;br&gt;④ 에틸렌은 28 이다.</t>
+          <t>① 아세틸렌은 분자량 26이다.&lt;br&gt;③ 부탄은 58로 가장 무겁다.&lt;br&gt;④ 에틸렌은 28이다.</t>
         </is>
       </c>
       <c r="AI84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;증기비중&lt;/strong&gt;&lt;br&gt;$\text{증기비중} = \dfrac{\text{분자량}}{29}$ 다. &lt;strong&gt;1 보다 작으면 위로 흩어지고, 크면 바닥에 깔린다&lt;/strong&gt;. &lt;strong&gt;부탄처럼 무거운 가스는 낮은 곳에 고여&lt;/strong&gt; 더 위험하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수소가 가장 가볍다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;증기비중&lt;/strong&gt;&lt;br&gt;$\text{증기비중} = \dfrac{\text{분자량}}{29}$다. &lt;strong&gt;1보다 작으면 위로 흩어지고, 크면 바닥에 깔린다&lt;/strong&gt;. &lt;strong&gt;부탄처럼 무거운 가스는 낮은 곳에 고여&lt;/strong&gt; 더 위험하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수소가 가장 가볍다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12188,7 @@
       </c>
       <c r="AI86" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자기연소(내부연소)&lt;/strong&gt;&lt;br&gt;자기연소 물질은 &lt;strong&gt;공기를 끊는 질식소화가 통하지 않는다&lt;/strong&gt;. &lt;strong&gt;스스로 산소를 지니고 있기&lt;/strong&gt; 때문이다. 그래서 &lt;strong&gt;다량의 물로 냉각소화&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제 산소로 타면 자기연소&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자기연소(내부연소)&lt;/strong&gt;&lt;br&gt;자기연소 물질은 &lt;strong&gt;공기를 끊는 질식소화가 통하지 않는다&lt;/strong&gt;. &lt;strong&gt;스스로 산소를 지니고 있기&lt;/strong&gt; 때문이다. 그래서 &lt;strong&gt;다량의 물로 냉각소화&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제 산소로 타면 자기연소&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12695,7 +12699,7 @@
       </c>
       <c r="AH90" s="32" t="inlineStr">
         <is>
-          <t>① 수소는 하한이 4 [vol%] 다.&lt;br&gt;② 메탄은 5 [vol%] 다.&lt;br&gt;③ 일산화탄소는 12.5 [vol%] 로 가장 높다.</t>
+          <t>① 수소는 하한이 4 [vol%]다.&lt;br&gt;② 메탄은 5 [vol%]다.&lt;br&gt;③ 일산화탄소는 12.5 [vol%]로 가장 높다.</t>
         </is>
       </c>
       <c r="AI90" s="32" t="inlineStr">
@@ -12948,7 +12952,7 @@
       </c>
       <c r="AG92" s="32" t="inlineStr">
         <is>
-          <t>마그네슘 화재에 &lt;strong&gt;물과 이산화탄소를 쓰면 안 된다&lt;/strong&gt;. 물과는 $\mathrm{Mg} + 2 H_{2} O \rightarrow \mathrm{Mg} ( OH )_{2} + H_{2}$ 로 수소를, 이산화탄소와는 $2 \mathrm{Mg} + CO_{2} \rightarrow 2 \mathrm{MgO} + C$ 로 반응해 &lt;strong&gt;오히려 불을 키운다&lt;/strong&gt;.</t>
+          <t>마그네슘 화재에 &lt;strong&gt;물과 이산화탄소를 쓰면 안 된다&lt;/strong&gt;. 물과는 $\mathrm{Mg} + 2 H_{2} O \rightarrow \mathrm{Mg} ( OH )_{2} + H_{2}$로 수소를, 이산화탄소와는 $2 \mathrm{Mg} + CO_{2} \rightarrow 2 \mathrm{MgO} + C$로 반응해 &lt;strong&gt;오히려 불을 키운다&lt;/strong&gt;.</t>
         </is>
       </c>
       <c r="AH92" s="32" t="inlineStr">
@@ -13043,7 +13047,7 @@
       </c>
       <c r="U93" s="32" t="inlineStr">
         <is>
-          <t>(보기) 의 물질을 폭발 범위가 넓은 것부터 좁은 순서로 바르게 배열한 것은?</t>
+          <t>(보기)의 물질을 폭발 범위가 넓은 것부터 좁은 순서로 바르게 배열한 것은?</t>
         </is>
       </c>
       <c r="V93" s="32" t="inlineStr">
@@ -13086,7 +13090,7 @@
       </c>
       <c r="AH93" s="32" t="inlineStr">
         <is>
-          <t>① CO 의 폭은 61.5 로 수소보다 좁다.&lt;br&gt;③ 프로판이 가장 좁으므로 맨 앞에 올 수 없다.&lt;br&gt;④ 메탄은 셋째다.</t>
+          <t>① CO의 폭은 61.5로 수소보다 좁다.&lt;br&gt;③ 프로판이 가장 좁으므로 맨 앞에 올 수 없다.&lt;br&gt;④ 메탄은 셋째다.</t>
         </is>
       </c>
       <c r="AI93" s="32" t="inlineStr">
@@ -13210,7 +13214,7 @@
       </c>
       <c r="AG94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;공업용 유기용제&lt;/strong&gt;는 제외 대상이 아니다. MSDS 를 갖추어야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;MSDS 작성·비치 제외 대상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;제외 대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원자력안전법에 따른 방사성 물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다른 법이 더 엄하게 다룬다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;농약관리법에 따른 농약&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 이유&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비료관리법에 따른 비료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 이유&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;약사법에 따른 의약품·의약외품&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 이유&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화장품법에 따른 화장품 · 식품위생법에 따른 식품&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 이유&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폐기물관리법에 따른 폐기물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 이유&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;공업용 유기용제&lt;/strong&gt;는 제외 대상이 아니다. MSDS를 갖추어야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;MSDS 작성·비치 제외 대상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;제외 대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원자력안전법에 따른 방사성 물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다른 법이 더 엄하게 다룬다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;농약관리법에 따른 농약&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 이유&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비료관리법에 따른 비료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 이유&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;약사법에 따른 의약품·의약외품&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 이유&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화장품법에 따른 화장품 · 식품위생법에 따른 식품&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 이유&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폐기물관리법에 따른 폐기물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 이유&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH94" s="32" t="inlineStr">
@@ -13950,7 +13954,7 @@
       </c>
       <c r="U100" s="32" t="inlineStr">
         <is>
-          <t>헥산 1vol%, 메탄 2vol%, 에틸렌 2vol%, 공기 95vol%로 된 혼합가스의 폭발하한계 값(vol%)은 약 얼마인가? (단, 헥산, 메탄, 에틸렌의 폭발하한계 값은 각각 1.1, 5.0, 2.7vol% 이다.)</t>
+          <t>헥산 1vol%, 메탄 2vol%, 에틸렌 2vol%, 공기 95vol%로 된 혼합가스의 폭발하한계 값(vol%)은 약 얼마인가? (단, 헥산, 메탄, 에틸렌의 폭발하한계 값은 각각 1.1, 5.0, 2.7vol%이다.)</t>
         </is>
       </c>
       <c r="V100" s="32" t="inlineStr"/>
@@ -13984,17 +13988,17 @@
       </c>
       <c r="AG100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가연성 가스만으로 다시 비율을 잡는다&lt;/strong&gt;. 합이 5 [vol%] 이므로 헥산 20, 메탄 40, 에틸렌 40 [%] 다. $\dfrac{100}{L} = \dfrac{20}{1.1} + \dfrac{40}{5.0} + \dfrac{40}{2.7} = 18.18 + 8 + 14.81 = 40.99$ 이므로 $L = 100 / 40.99 \fallingdotseq 2.44$ [vol%] 다.</t>
+          <t>&lt;strong&gt;가연성 가스만으로 다시 비율을 잡는다&lt;/strong&gt;. 합이 5 [vol%]이므로 헥산 20, 메탄 40, 에틸렌 40 [%]다. $\dfrac{100}{L} = \dfrac{20}{1.1} + \dfrac{40}{5.0} + \dfrac{40}{2.7} = 18.18 + 8 + 14.81 = 40.99$이므로 $L = 100 / 40.99 \fallingdotseq 2.44$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH100" s="32" t="inlineStr">
         <is>
-          <t>② 12.89 는 공기를 뺀 환산을 하지 않았을 때 나오는 값이다.&lt;br&gt;③ 21.78 도 계산과 맞지 않는다.&lt;br&gt;④ 48.78 도 맞지 않는다.</t>
+          <t>② 12.89는 공기를 뺀 환산을 하지 않았을 때 나오는 값이다.&lt;br&gt;③ 21.78 도 계산과 맞지 않는다.&lt;br&gt;④ 48.78 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;르 샤틀리에(Le Chatelier)의 법칙&lt;/strong&gt;&lt;br&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$ 다. &lt;strong&gt;공기가 섞여 있으면 반드시 가연성 가스끼리 다시 100 [%] 로 환산&lt;/strong&gt; 한 뒤에 넣어야 한다. 이 한 단계를 건너뛰면 12.89 를 골라 틀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기를 빼고 다시 100 [%] 로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;르 샤틀리에(Le Chatelier)의 법칙&lt;/strong&gt;&lt;br&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$다. &lt;strong&gt;공기가 섞여 있으면 반드시 가연성 가스끼리 다시 100 [%]로 환산&lt;/strong&gt;한 뒤에 넣어야 한다. 이 한 단계를 건너뛰면 12.89를 골라 틀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기를 빼고 다시 100 [%]로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14083,7 @@
       </c>
       <c r="U101" s="32" t="inlineStr">
         <is>
-          <t>에틸에테르와 에틸알콜이 3:1로 혼합증기의 몰비가 각각 0.75, 0.25 이고, 에틸에테르와 에틸알콜의 폭발하한값이 각각 1.9vol%, 4.3vol%일 때 혼합가스의 폭발하한값은 약 몇 vol%인가?</t>
+          <t>에틸에테르와 에틸알콜이 3:1로 혼합증기의 몰비가 각각 0.75, 0.25이고, 에틸에테르와 에틸알콜의 폭발하한값이 각각 1.9vol%, 4.3vol%일 때 혼합가스의 폭발하한값은 약 몇 vol%인가?</t>
         </is>
       </c>
       <c r="V101" s="32" t="inlineStr"/>
@@ -14113,12 +14117,12 @@
       </c>
       <c r="AG101" s="32" t="inlineStr">
         <is>
-          <t>$\dfrac{100}{L} = \dfrac{75}{1.9} + \dfrac{25}{4.3} = 39.47 + 5.81 = 45.28$ 이므로 $L = 100 / 45.28 \fallingdotseq 2.21$ [vol%] 다.</t>
+          <t>$\dfrac{100}{L} = \dfrac{75}{1.9} + \dfrac{25}{4.3} = 39.47 + 5.81 = 45.28$이므로 $L = 100 / 45.28 \fallingdotseq 2.21$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH101" s="32" t="inlineStr">
         <is>
-          <t>② 3.5 [vol%] 는 계산과 맞지 않는다.&lt;br&gt;③ 22.0 [vol%] 는 자릿수가 열 배 어긋난다.&lt;br&gt;④ 34.7 [vol%] 도 맞지 않는다.</t>
+          <t>② 3.5 [vol%]는 계산과 맞지 않는다.&lt;br&gt;③ 22.0 [vol%]는 자릿수가 열 배 어긋난다.&lt;br&gt;④ 34.7 [vol%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI101" s="32" t="inlineStr">
@@ -14242,12 +14246,12 @@
       </c>
       <c r="AG102" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;비등액 팽창증기 폭발(Boiling Liquid Expanding Vapor Explosion)&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;BLEVE 와 UVCE&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;BLEVE&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;UVCE&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;이름&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비등액 팽창증기 폭발&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개방계 증기운 폭발&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;언제&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;액화가스 탱크가 불에 달구어져 터질 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;새어 나온 가연성 증기가 구름을 이룬 뒤 점화될 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;결과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파이어볼(fire ball)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;폭풍압에 의한 넓은 피해&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;대책&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;탱크에 물을 뿌려 식힌다 · 방액제 · 단열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;누출 감지 · 발화원 관리&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;비등액 팽창증기 폭발(Boiling Liquid Expanding Vapor Explosion)&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;BLEVE와 UVCE&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;BLEVE&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;UVCE&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;이름&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비등액 팽창증기 폭발&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개방계 증기운 폭발&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;언제&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;액화가스 탱크가 불에 달구어져 터질 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;새어 나온 가연성 증기가 구름을 이룬 뒤 점화될 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;결과&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;파이어볼(fire ball)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;폭풍압에 의한 넓은 피해&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;대책&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;탱크에 물을 뿌려 식힌다 · 방액제 · 단열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;누출 감지 · 발화원 관리&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH102" s="32" t="inlineStr">
         <is>
-          <t>① 고농도 분진폭발은 BLEVE 와 관계없다.&lt;br&gt;② 저농도의 분해폭발도 그렇다.&lt;br&gt;③ 개방계 증기운 폭발은 UVCE 다.</t>
+          <t>① 고농도 분진폭발은 BLEVE와 관계없다.&lt;br&gt;② 저농도의 분해폭발도 그렇다.&lt;br&gt;③ 개방계 증기운 폭발은 UVCE다.</t>
         </is>
       </c>
       <c r="AI102" s="32" t="inlineStr">
@@ -14767,12 +14771,12 @@
       </c>
       <c r="AH106" s="32" t="inlineStr">
         <is>
-          <t>① 15 [cm] 는 발판으로 너무 좁다.&lt;br&gt;② 20 [cm] 도 기준에 못 미친다.&lt;br&gt;④ 60 [cm] 는 기준보다 넓다.</t>
+          <t>① 15 [cm]는 발판으로 너무 좁다.&lt;br&gt;② 20 [cm] 도 기준에 못 미친다.&lt;br&gt;④ 60 [cm]는 기준보다 넓다.</t>
         </is>
       </c>
       <c r="AI106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제63조 — 달비계의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;작업발판의 폭은 어디서든 40 [cm] 이상&lt;/strong&gt;이 기본이다. 다만 &lt;strong&gt;달비계만은 틈새를 「3 [cm] 이하」가 아니라 「없도록」&lt;/strong&gt; 해야 한다 — 아래가 허공이기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업발판은 40 [cm] 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C63%EC%A1%B0" target="_blank"&gt;제63조(달비계의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 곤돌라형 달비계를 설치하는 경우에는 다음 각 호의 사항을 준수해야 한다. &amp;lt;개정 2021.11.19&amp;gt;&lt;br&gt; 1. 다음 각 목의 어느 하나에 해당하는 와이어로프를 달비계에 사용해서는 아니 된다.&lt;br&gt; 가. 이음매가 있는 것&lt;br&gt; 나. 와이어로프의 한 꼬임[(스트랜드(strand)를 말한다. 이하 같다)]에서 끊어진 소선(素線)[필러(pillar)선은 제외한다)]의 수가 10퍼센트 이상(비자전로프의 경우에는 끊어진 소선의 수가 와이어로프 호칭지름의 6배 길이 이내에서 4개 이상이거나 호칭지름 30배 길이 이내에서 8개 이상)인 것&lt;br&gt; 다. 지름의 감소가 공칭지름의 7퍼센트를 초과하는 것&lt;br&gt; 라. 꼬인 것&lt;br&gt; 마. 심하게 변형되거나 부식된 것&lt;br&gt; 바. 열과 전기충격에 의해 손상된 것&lt;br&gt; 2. 다음 각 목의 어느 하나에 해당하는 달기 체인을 달비계에 사용해서는 아니 된다.&lt;br&gt; 가. 달기 체인의 길이가 달기 체인이 제조된 때의 길이의 5퍼센트를 초과한 것&lt;br&gt; 나. 링의 단면지름이 달기 체인이 제조된 때의 해당 링의 지름의 10퍼센트를 초과하여 감소한 것&lt;br&gt; 다. 균열이 있거나 심하게 변형된 것&lt;br&gt; 3. 삭제&amp;lt;2021.11.19&amp;gt;&lt;br&gt; 4. 달기 강선 및 달기 강대는 심하게 손상ㆍ변형 또는 부식된 것을 사용하지 않도록 할 것&lt;br&gt; 5. 달기 와이어로프, 달기 체인, 달기 강선, 달기 강대는 한쪽 끝을 비계의 보 등에, 다른 쪽 끝을 내민 보, 앵커볼트 또는 건축물의 보 등에 각각 풀리지 않도록 설치할 것&lt;br&gt;▶  6. 작업발판은 폭을 &lt;strong&gt;40센티미터&lt;/strong&gt; 이상으로 하고 틈새가 없도록 할 것&lt;br&gt; 7. 작업발판의 재료는 뒤집히거나 떨어지지 않도록 비계의 보 등에 연결하거나 고정시킬 것&lt;br&gt; 8. 비계가 흔들리거나 뒤집히는 것을 방지하기 위하여 비계의 보ㆍ작업발판 등에 버팀을 설치하는 등 필요한 조치를 할 것&lt;br&gt; 9. 선반 비계에서는 보의 접속부 및 교차부를 철선ㆍ이음철물 등을 사용하여 확실하게 접속시키거나 단단하게 연결시킬 것&lt;br&gt; 10. 근로자의 추락 위험을 방지하기 위하여 다음 각 목의 조치를 할 것&lt;br&gt; 가. 달비계에 구명줄을 설치할 것&lt;br&gt; 나. 근로자에게 안전대를 착용하도록 하고 근로자가 착용한 안전줄을 달비계의 구명줄에 체결(締結)하도록 할 것&lt;br&gt; 다. 달비계에 안전난간을 설치할 수 있는 구조인 경우에는 달비계에 안전난간을 설치할 것&lt;br&gt;② 사업주는 작업의자형 달비계를 설치하는 경우에는 다음 각 호의 사항을 준수해야 한다. &amp;lt;신설 2021.11.19&amp;gt;&lt;br&gt; 1. 달비계의 작업대는 나무 등 근로자의 하중을 견딜 수 있는 강도의 재료를 사용하여 견고한 구조로 제작할 것&lt;br&gt; 2. 작업대의 4개 모서리에 로프를 매달아 작업대가 뒤집히거나 떨어지지 않도록 연결할 것&lt;br&gt; 3. 작업용 섬유로프는 콘크리트에 매립된 고리, 건축물의 콘크리트 또는 철재 구조물 등 2개 이상의 견고한 고정점에 풀리지 않도록 결속(結束)할 것&lt;br&gt; 4. 작업용 섬유로프와 구명줄은 다른 고정점에 결속되도록 할 것&lt;br&gt; 5. 작업하는 근로자의 하중을 견딜 수 있을 정도의 강도를 가진 작업용 섬유로프, 구명줄 및 고정점을 사용할 것&lt;br&gt; 6. 근로자가 작업용 섬유로프에 작업대를 연결하여 하강하는 방법으로 작업을 하는 경우 근로자의 조종 없이는 작업대가 하강하지 않도록 할 것&lt;br&gt; 7. 작업용 섬유로프 또는 구명줄이 결속된 고정점의 로프는 다른 사람이 풀지 못하게 하고 작업 중임을 알리는 경고표지를 부착할 것&lt;br&gt; 8. 작업용 섬유로프와 구명줄이 건물이나 구조물의 끝부분, 날카로운 물체 등에 의하여 절단되거나 마모(磨耗)될 우려가 있는 경우에는 로프에 이를 방지할 수 있는 보호 덮개를 씌우는 등의 조치를 할 것&lt;br&gt; 9. 달비계에 다음 각 목의 작업용 섬유로프 또는 안전대의 섬유벨트를 사용하지 않을 것&lt;br&gt; 가. 꼬임이 끊어진 것&lt;br&gt; 나. 심하게 손상되거나 부식된 것&lt;br&gt; 다. 2개 이상의 작업용 섬유로프 또는 섬유벨트를 연결한 것&lt;br&gt; 라. 작업높이보다 길이가 짧은 것&lt;br&gt; 10. 근로자의 추락 위험을 방지하기 위하여 다음 각 목의 조치를 할 것&lt;br&gt; 가. 달비계에 구명줄을 설치할 것&lt;br&gt; 나. 근로자에게 안전대를 착용하도록 하고 근로자가 착용한 안전줄을 달비계의 구명줄에 체결(締結)하도록 할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제63조 — 달비계의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;작업발판의 폭은 어디서든 40 [cm] 이상&lt;/strong&gt;이 기본이다. 다만 &lt;strong&gt;달비계만은 틈새를 「3 [cm] 이하」가 아니라 「없도록」&lt;/strong&gt;해야 한다 — 아래가 허공이기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업발판은 40 [cm] 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C63%EC%A1%B0" target="_blank"&gt;제63조(달비계의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 곤돌라형 달비계를 설치하는 경우에는 다음 각 호의 사항을 준수해야 한다. &amp;lt;개정 2021.11.19&amp;gt;&lt;br&gt; 1. 다음 각 목의 어느 하나에 해당하는 와이어로프를 달비계에 사용해서는 아니 된다.&lt;br&gt; 가. 이음매가 있는 것&lt;br&gt; 나. 와이어로프의 한 꼬임[(스트랜드(strand)를 말한다. 이하 같다)]에서 끊어진 소선(素線)[필러(pillar)선은 제외한다)]의 수가 10퍼센트 이상(비자전로프의 경우에는 끊어진 소선의 수가 와이어로프 호칭지름의 6배 길이 이내에서 4개 이상이거나 호칭지름 30배 길이 이내에서 8개 이상)인 것&lt;br&gt; 다. 지름의 감소가 공칭지름의 7퍼센트를 초과하는 것&lt;br&gt; 라. 꼬인 것&lt;br&gt; 마. 심하게 변형되거나 부식된 것&lt;br&gt; 바. 열과 전기충격에 의해 손상된 것&lt;br&gt; 2. 다음 각 목의 어느 하나에 해당하는 달기 체인을 달비계에 사용해서는 아니 된다.&lt;br&gt; 가. 달기 체인의 길이가 달기 체인이 제조된 때의 길이의 5퍼센트를 초과한 것&lt;br&gt; 나. 링의 단면지름이 달기 체인이 제조된 때의 해당 링의 지름의 10퍼센트를 초과하여 감소한 것&lt;br&gt; 다. 균열이 있거나 심하게 변형된 것&lt;br&gt; 3. 삭제&amp;lt;2021.11.19&amp;gt;&lt;br&gt; 4. 달기 강선 및 달기 강대는 심하게 손상ㆍ변형 또는 부식된 것을 사용하지 않도록 할 것&lt;br&gt; 5. 달기 와이어로프, 달기 체인, 달기 강선, 달기 강대는 한쪽 끝을 비계의 보 등에, 다른 쪽 끝을 내민 보, 앵커볼트 또는 건축물의 보 등에 각각 풀리지 않도록 설치할 것&lt;br&gt;▶  6. 작업발판은 폭을 &lt;strong&gt;40센티미터&lt;/strong&gt; 이상으로 하고 틈새가 없도록 할 것&lt;br&gt; 7. 작업발판의 재료는 뒤집히거나 떨어지지 않도록 비계의 보 등에 연결하거나 고정시킬 것&lt;br&gt; 8. 비계가 흔들리거나 뒤집히는 것을 방지하기 위하여 비계의 보ㆍ작업발판 등에 버팀을 설치하는 등 필요한 조치를 할 것&lt;br&gt; 9. 선반 비계에서는 보의 접속부 및 교차부를 철선ㆍ이음철물 등을 사용하여 확실하게 접속시키거나 단단하게 연결시킬 것&lt;br&gt; 10. 근로자의 추락 위험을 방지하기 위하여 다음 각 목의 조치를 할 것&lt;br&gt; 가. 달비계에 구명줄을 설치할 것&lt;br&gt; 나. 근로자에게 안전대를 착용하도록 하고 근로자가 착용한 안전줄을 달비계의 구명줄에 체결(締結)하도록 할 것&lt;br&gt; 다. 달비계에 안전난간을 설치할 수 있는 구조인 경우에는 달비계에 안전난간을 설치할 것&lt;br&gt;② 사업주는 작업의자형 달비계를 설치하는 경우에는 다음 각 호의 사항을 준수해야 한다. &amp;lt;신설 2021.11.19&amp;gt;&lt;br&gt; 1. 달비계의 작업대는 나무 등 근로자의 하중을 견딜 수 있는 강도의 재료를 사용하여 견고한 구조로 제작할 것&lt;br&gt; 2. 작업대의 4개 모서리에 로프를 매달아 작업대가 뒤집히거나 떨어지지 않도록 연결할 것&lt;br&gt; 3. 작업용 섬유로프는 콘크리트에 매립된 고리, 건축물의 콘크리트 또는 철재 구조물 등 2개 이상의 견고한 고정점에 풀리지 않도록 결속(結束)할 것&lt;br&gt; 4. 작업용 섬유로프와 구명줄은 다른 고정점에 결속되도록 할 것&lt;br&gt; 5. 작업하는 근로자의 하중을 견딜 수 있을 정도의 강도를 가진 작업용 섬유로프, 구명줄 및 고정점을 사용할 것&lt;br&gt; 6. 근로자가 작업용 섬유로프에 작업대를 연결하여 하강하는 방법으로 작업을 하는 경우 근로자의 조종 없이는 작업대가 하강하지 않도록 할 것&lt;br&gt; 7. 작업용 섬유로프 또는 구명줄이 결속된 고정점의 로프는 다른 사람이 풀지 못하게 하고 작업 중임을 알리는 경고표지를 부착할 것&lt;br&gt; 8. 작업용 섬유로프와 구명줄이 건물이나 구조물의 끝부분, 날카로운 물체 등에 의하여 절단되거나 마모(磨耗)될 우려가 있는 경우에는 로프에 이를 방지할 수 있는 보호 덮개를 씌우는 등의 조치를 할 것&lt;br&gt; 9. 달비계에 다음 각 목의 작업용 섬유로프 또는 안전대의 섬유벨트를 사용하지 않을 것&lt;br&gt; 가. 꼬임이 끊어진 것&lt;br&gt; 나. 심하게 손상되거나 부식된 것&lt;br&gt; 다. 2개 이상의 작업용 섬유로프 또는 섬유벨트를 연결한 것&lt;br&gt; 라. 작업높이보다 길이가 짧은 것&lt;br&gt; 10. 근로자의 추락 위험을 방지하기 위하여 다음 각 목의 조치를 할 것&lt;br&gt; 가. 달비계에 구명줄을 설치할 것&lt;br&gt; 나. 근로자에게 안전대를 착용하도록 하고 근로자가 착용한 안전줄을 달비계의 구명줄에 체결(締結)하도록 할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -15025,7 +15029,7 @@
       </c>
       <c r="AH108" s="32" t="inlineStr">
         <is>
-          <t>① 달기체인의 안전계수는 10 이 아니라 5 이상이다.&lt;br&gt;② 목재는 2.5 가 아니라 5 이상이다. 2.5 는 강재의 값이다.&lt;br&gt;③ 달기와이어로프는 5 가 아니라 10 이상이다.</t>
+          <t>① 달기체인의 안전계수는 10이 아니라 5 이상이다.&lt;br&gt;② 목재는 2.5가 아니라 5 이상이다. 2.5는 강재의 값이다.&lt;br&gt;③ 달기와이어로프는 5가 아니라 10 이상이다.</t>
         </is>
       </c>
       <c r="AI108" s="32" t="inlineStr">
@@ -15417,7 +15421,7 @@
       </c>
       <c r="AI111" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;비탈면의 안정&lt;/strong&gt;&lt;br&gt;비탈면의 안전율은 $\dfrac{\text{버티는 힘}}{\text{미끄러지려는}} \text{힘}$ 이다. &lt;strong&gt;위를 덜어 내면 미끄러지려는 힘이 줄고, 아래를 쌓으면 버티는 힘이 는다&lt;/strong&gt;. &lt;strong&gt;위에 쌓는 것만 정반대&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;위는 덜고 아래는 쌓는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;비탈면의 안정&lt;/strong&gt;&lt;br&gt;비탈면의 안전율은 $\dfrac{\text{버티는 힘}}{\text{미끄러지려는}} \text{힘}$이다. &lt;strong&gt;위를 덜어 내면 미끄러지려는 힘이 줄고, 아래를 쌓으면 버티는 힘이 는다&lt;/strong&gt;. &lt;strong&gt;위에 쌓는 것만 정반대&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;위는 덜고 아래는 쌓는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15808,7 +15812,7 @@
       </c>
       <c r="AI114" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제24조 — 사다리식 통로 등의 구조&lt;/strong&gt;&lt;br&gt;네 숫자를 묶어 둔다 — &lt;strong&gt;벽에서 15, 위로 60, 기울기 75°, 등받이울 7 [m]/2.5 [m]&lt;/strong&gt;. &lt;strong&gt;「60 [cm] 이상 올라가게」&lt;/strong&gt;는 오르내릴 때 손으로 잡기 위한 것이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;상단은 60 [cm] 이상 올라가게&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 고정식 사다리의 등받이울 규정은 &lt;u&gt;2024. 6. 28. 개정&lt;/u&gt;으로 바뀌어, &lt;u&gt;높이 7 [m] 이상이면 바닥에서 2.5 [m] 되는 지점부터 등받이울을 설치&lt;/u&gt; 하되 &lt;u&gt;등받이울 대신 개인용 추락방지 시스템을 설치할 수 있는 근거&lt;/u&gt;가 들어갔다. 다만 여기서 묻는 &lt;u&gt;상단 60 [cm]&lt;/u&gt;는 개정과 무관하다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C24%EC%A1%B0" target="_blank"&gt;제24조(사다리식 통로 등의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ ① 사업주는 사다리식 통로 등을 설치하는 경우 다음 각 호의 사항을 준수하여야 한다. &amp;lt;개정 &lt;strong&gt;2024.6.&lt;/strong&gt;28&amp;gt;&lt;br&gt; 1. 견고한 구조로 할 것&lt;br&gt; 2. 심한 손상ㆍ부식 등이 없는 재료를 사용할 것&lt;br&gt; 3. 발판의 간격은 일정하게 할 것&lt;br&gt; 4. 발판과 벽과의 사이는 15센티미터 이상의 간격을 유지할 것&lt;br&gt; 5. 폭은 30센티미터 이상으로 할 것&lt;br&gt; 6. 사다리가 넘어지거나 미끄러지는 것을 방지하기 위한 조치를 할 것&lt;br&gt; 7. 사다리의 상단은 걸쳐놓은 지점으로부터 60센티미터 이상 올라가도록 할 것&lt;br&gt; 8. 사다리식 통로의 길이가 10미터 이상인 경우에는 5미터 이내마다 계단참을 설치할 것&lt;br&gt; 9. 사다리식 통로의 기울기는 75도 이하로 할 것. 다만, 고정식 사다리식 통로의 기울기는 90도 이하로 하고, 그 높이가 7미터 이상인 경우에는 다음 각 목의 구분에 따른 조치를 할 것&lt;br&gt;▶  가. 등받이울이 있어도 근로자 이동에 지장이 없는 경우: 바닥으로부터 높이가 2.5미터 &lt;strong&gt;되는 지점부터 등받이울을 설치&lt;/strong&gt;할 것&lt;br&gt;▶  나. 등받이울이 있으면 근로자가 이동이 곤란한 경우: 한국산업표준에서 정하는 기준에 적합한 &lt;strong&gt;개인용 추락 방지 시스템을&lt;/strong&gt; 설치하고 근로자로 하여금 한국산업표준에서 정하는 기준에 적합한 전신안전대를 사용하도록 할 것&lt;br&gt; 10. 접이식 사다리 기둥은 사용 시 접혀지거나 펼쳐지지 않도록 철물 등을 사용하여 견고하게 조치할 것&lt;br&gt;② 잠함(潛函) 내 사다리식 통로와 건조ㆍ수리 중인 선박의 구명줄이 설치된 사다리식 통로(건조ㆍ수리작업을 위하여 임시로 설치한 사다리식 통로는 제외한다)에 대해서는 제1항제5호부터 제10호까지의 규정을 적용하지 아니한다.&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제24조 — 사다리식 통로 등의 구조&lt;/strong&gt;&lt;br&gt;네 숫자를 묶어 둔다 — &lt;strong&gt;벽에서 15, 위로 60, 기울기 75°, 등받이울 7 [m]/2.5 [m]&lt;/strong&gt;. &lt;strong&gt;「60 [cm] 이상 올라가게」&lt;/strong&gt;는 오르내릴 때 손으로 잡기 위한 것이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;상단은 60 [cm] 이상 올라가게&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 고정식 사다리의 등받이울 규정은 &lt;u&gt;2024. 6. 28. 개정&lt;/u&gt;으로 바뀌어, &lt;u&gt;높이 7 [m] 이상이면 바닥에서 2.5 [m] 되는 지점부터 등받이울을 설치&lt;/u&gt;하되 &lt;u&gt;등받이울 대신 개인용 추락방지 시스템을 설치할 수 있는 근거&lt;/u&gt;가 들어갔다. 다만 여기서 묻는 &lt;u&gt;상단 60 [cm]&lt;/u&gt;는 개정과 무관하다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C24%EC%A1%B0" target="_blank"&gt;제24조(사다리식 통로 등의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ ① 사업주는 사다리식 통로 등을 설치하는 경우 다음 각 호의 사항을 준수하여야 한다. &amp;lt;개정 &lt;strong&gt;2024.6.&lt;/strong&gt;28&amp;gt;&lt;br&gt; 1. 견고한 구조로 할 것&lt;br&gt; 2. 심한 손상ㆍ부식 등이 없는 재료를 사용할 것&lt;br&gt; 3. 발판의 간격은 일정하게 할 것&lt;br&gt; 4. 발판과 벽과의 사이는 15센티미터 이상의 간격을 유지할 것&lt;br&gt; 5. 폭은 30센티미터 이상으로 할 것&lt;br&gt; 6. 사다리가 넘어지거나 미끄러지는 것을 방지하기 위한 조치를 할 것&lt;br&gt; 7. 사다리의 상단은 걸쳐놓은 지점으로부터 60센티미터 이상 올라가도록 할 것&lt;br&gt; 8. 사다리식 통로의 길이가 10미터 이상인 경우에는 5미터 이내마다 계단참을 설치할 것&lt;br&gt; 9. 사다리식 통로의 기울기는 75도 이하로 할 것. 다만, 고정식 사다리식 통로의 기울기는 90도 이하로 하고, 그 높이가 7미터 이상인 경우에는 다음 각 목의 구분에 따른 조치를 할 것&lt;br&gt;▶  가. 등받이울이 있어도 근로자 이동에 지장이 없는 경우: 바닥으로부터 높이가 2.5미터 &lt;strong&gt;되는 지점부터 등받이울을 설치&lt;/strong&gt;할 것&lt;br&gt;▶  나. 등받이울이 있으면 근로자가 이동이 곤란한 경우: 한국산업표준에서 정하는 기준에 적합한 &lt;strong&gt;개인용 추락 방지 시스템을&lt;/strong&gt; 설치하고 근로자로 하여금 한국산업표준에서 정하는 기준에 적합한 전신안전대를 사용하도록 할 것&lt;br&gt; 10. 접이식 사다리 기둥은 사용 시 접혀지거나 펼쳐지지 않도록 철물 등을 사용하여 견고하게 조치할 것&lt;br&gt;② 잠함(潛函) 내 사다리식 통로와 건조ㆍ수리 중인 선박의 구명줄이 설치된 사다리식 통로(건조ㆍ수리작업을 위하여 임시로 설치한 사다리식 통로는 제외한다)에 대해서는 제1항제5호부터 제10호까지의 규정을 적용하지 아니한다.&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -16056,12 +16060,12 @@
       </c>
       <c r="AG116" s="32" t="inlineStr">
         <is>
-          <t>냉동·냉장창고시설의 설비공사는 &lt;strong&gt;연면적 5,000 [㎡] 이상&lt;/strong&gt; 이라야 대상이다. 3,000 [㎡] 는 못 미친다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건설공사 계획서 제출 대상 (영 제42조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상 공사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지상높이 31 [m] 이상인 건축물 또는 인공구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 3만 [㎡] 이상인 건축물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;연면적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 5천 [㎡] 이상인 문화·집회시설, 판매·운수시설, 종교시설, 의료시설 중 종합병원, 숙박시설 중 관광숙박시설, 지하도상가, 냉동·냉장 창고시설&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5천 [㎡]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 5천 [㎡] 이상인 냉동·냉장 창고시설의 설비공사 및 단열공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 지간길이 50 [m] 이상인 교량 건설공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널 건설공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;크기와 무관&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다목적댐·발전용댐, 저수용량 2천만 [t] 이상의 용수 전용댐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;깊이 10 [m] 이상인 굴착공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>냉동·냉장창고시설의 설비공사는 &lt;strong&gt;연면적 5,000 [㎡] 이상&lt;/strong&gt;이라야 대상이다. 3,000 [㎡]는 못 미친다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건설공사 계획서 제출 대상 (영 제42조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상 공사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지상높이 31 [m] 이상인 건축물 또는 인공구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 3만 [㎡] 이상인 건축물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;연면적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 5천 [㎡] 이상인 문화·집회시설, 판매·운수시설, 종교시설, 의료시설 중 종합병원, 숙박시설 중 관광숙박시설, 지하도상가, 냉동·냉장 창고시설&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5천 [㎡]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 5천 [㎡] 이상인 냉동·냉장 창고시설의 설비공사 및 단열공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 지간길이 50 [m] 이상인 교량 건설공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널 건설공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;크기와 무관&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다목적댐·발전용댐, 저수용량 2천만 [t] 이상의 용수 전용댐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;깊이 10 [m] 이상인 굴착공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH116" s="32" t="inlineStr">
         <is>
-          <t>① 지상높이 50 [m] 는 31 [m] 이상이므로 대상이다.&lt;br&gt;③ 최대 지간길이 60 [m] 는 50 [m] 이상이므로 대상이다.&lt;br&gt;④ 터널건설공사는 크기와 관계없이 대상이다.</t>
+          <t>① 지상높이 50 [m]는 31 [m] 이상이므로 대상이다.&lt;br&gt;③ 최대 지간길이 60 [m]는 50 [m] 이상이므로 대상이다.&lt;br&gt;④ 터널건설공사는 크기와 관계없이 대상이다.</t>
         </is>
       </c>
       <c r="AI116" s="32" t="inlineStr">
@@ -16194,7 +16198,7 @@
       </c>
       <c r="AH117" s="32" t="inlineStr">
         <is>
-          <t>① 20 [cm] 는 기준보다 촘촘하다.&lt;br&gt;③ 40 [cm] 는 기준보다 넓다.&lt;br&gt;④ 50 [cm] 도 그렇다.</t>
+          <t>① 20 [cm]는 기준보다 촘촘하다.&lt;br&gt;③ 40 [cm]는 기준보다 넓다.&lt;br&gt;④ 50 [cm] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI117" s="32" t="inlineStr">
@@ -16452,12 +16456,12 @@
       </c>
       <c r="AH119" s="32" t="inlineStr">
         <is>
-          <t>① 10 [m/s] 초과는 설치·해체 작업 중지 기준이다.&lt;br&gt;③ 25 [m/s] 라는 기준은 없다.&lt;br&gt;④ 30 [m/s] 초과는 이탈 방지 조치 기준이다.</t>
+          <t>① 10 [m/s] 초과는 설치·해체 작업 중지 기준이다.&lt;br&gt;③ 25 [m/s]라는 기준은 없다.&lt;br&gt;④ 30 [m/s] 초과는 이탈 방지 조치 기준이다.</t>
         </is>
       </c>
       <c r="AI119" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제37조 · 제140조 · 제154조&lt;/strong&gt;&lt;br&gt;네 숫자를 &lt;strong&gt;10 · 15 · 30 · 35&lt;/strong&gt;로 잡는다. &lt;strong&gt;올라가서 하는 일(설치·해체)이 10 으로 가장 낮고&lt;/strong&gt;, 숫자가 커질수록 &lt;strong&gt;운전 → 이탈 방지 → 붕괴 방지&lt;/strong&gt;로 옮겨 간다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;설치·해체 10, 운전 15&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제37조 · 제140조 · 제154조&lt;/strong&gt;&lt;br&gt;네 숫자를 &lt;strong&gt;10 · 15 · 30 · 35&lt;/strong&gt;로 잡는다. &lt;strong&gt;올라가서 하는 일(설치·해체)이 10으로 가장 낮고&lt;/strong&gt;, 숫자가 커질수록 &lt;strong&gt;운전 → 이탈 방지 → 붕괴 방지&lt;/strong&gt;로 옮겨 간다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;설치·해체 10, 운전 15&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16709,12 +16713,12 @@
       </c>
       <c r="AG121" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가늘고 고른 모래층&lt;/strong&gt; 이야말로 &lt;strong&gt;액상화가 가장 잘 일어나는&lt;/strong&gt; 지반이다. 그런 흙으로 바꾸는 것은 정반대다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;액상화가 잘 일어나는 조건과 대책&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;잘 일어나는 조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;입도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가늘고 고른(균등한) 모래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입도가 양호한 재료로 치환&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;밀도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느슨한 상태&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다져서 상대밀도를 높인다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;물&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지하수위가 높아 포화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;deep well 로 지하수위를 낮춘다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;가늘고 고른 모래층&lt;/strong&gt; 이야말로 &lt;strong&gt;액상화가 가장 잘 일어나는&lt;/strong&gt; 지반이다. 그런 흙으로 바꾸는 것은 정반대다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;액상화가 잘 일어나는 조건과 대책&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;잘 일어나는 조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;입도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가늘고 고른(균등한) 모래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입도가 양호한 재료로 치환&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;밀도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느슨한 상태&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다져서 상대밀도를 높인다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;물&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지하수위가 높아 포화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;deep well로 지하수위를 낮춘다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH121" s="32" t="inlineStr">
         <is>
-          <t>② 입도가 불량한 재료를 양호한 재료로 바꾸는 것은 옳은 대책이다.&lt;br&gt;③ deep well 로 지하수위를 낮추는 것도 그렇다.&lt;br&gt;④ 다져서 상대밀도를 높이는 것도 그렇다.</t>
+          <t>② 입도가 불량한 재료를 양호한 재료로 바꾸는 것은 옳은 대책이다.&lt;br&gt;③ deep well로 지하수위를 낮추는 것도 그렇다.&lt;br&gt;④ 다져서 상대밀도를 높이는 것도 그렇다.</t>
         </is>
       </c>
       <c r="AI121" s="32" t="inlineStr">
